--- a/output/preprocessed_data.xlsx
+++ b/output/preprocessed_data.xlsx
@@ -37388,34 +37388,34 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="B2" t="n">
-        <v>0.07054523274401214</v>
+        <v>0.01465427463960587</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.127074524045298</v>
+        <v>-0.09765692923147765</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08547458378412931</v>
+        <v>0.2290216444081314</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.035517793760804</v>
+        <v>-0.1293416997003018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8961795778339856</v>
+        <v>1.011182327339828</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.264432380032718</v>
+        <v>-0.3143755756434194</v>
       </c>
       <c r="H2" t="n">
-        <v>1.179614739538029</v>
+        <v>0.8083119552969112</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.8000004825507991</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.1999995174492008</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -37424,7 +37424,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.730170535430454e-06</v>
+        <v>4.825507992282845e-06</v>
       </c>
     </row>
   </sheetData>
@@ -37438,7 +37438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37494,12 +37494,12 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>ppc</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>oth</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ppc</t>
         </is>
       </c>
     </row>
@@ -37510,11 +37510,11 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -37524,24 +37524,26 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="G2" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H2" t="n">
         <v>0.06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K2" t="n">
         <v>0.01</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37550,11 +37552,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -37564,25 +37566,23 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H3" t="n">
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="J3" t="n">
         <v>0.02</v>
       </c>
-      <c r="K3" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="4">
@@ -37592,11 +37592,11 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -37606,23 +37606,25 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.403</v>
+        <v>0.41</v>
       </c>
       <c r="G4" t="n">
-        <v>0.328</v>
+        <v>0.32</v>
       </c>
       <c r="H4" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.132</v>
+        <v>0.16</v>
       </c>
       <c r="J4" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L4" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="5">
@@ -37632,11 +37634,11 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46166</v>
+        <v>46171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -37646,22 +37648,22 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.45</v>
+        <v>0.403</v>
       </c>
       <c r="G5" t="n">
-        <v>0.32</v>
+        <v>0.328</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="I5" t="n">
-        <v>0.11</v>
+        <v>0.132</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03</v>
+        <v>0.051</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -37672,11 +37674,11 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -37686,25 +37688,23 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="G6" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0.11</v>
       </c>
       <c r="J6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
         <v>0.02</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="7">
@@ -37714,11 +37714,11 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -37728,23 +37728,25 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.411</v>
+        <v>0.43</v>
       </c>
       <c r="G7" t="n">
-        <v>0.327</v>
+        <v>0.31</v>
       </c>
       <c r="H7" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.126</v>
+        <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="L7" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="8">
@@ -37754,11 +37756,11 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -37768,24 +37770,24 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.47</v>
+        <v>0.411</v>
       </c>
       <c r="G8" t="n">
-        <v>0.35</v>
+        <v>0.327</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08</v>
+        <v>0.126</v>
       </c>
       <c r="J8" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.02</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37794,11 +37796,11 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46158</v>
+        <v>46162</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -37808,26 +37810,24 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="G9" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="H9" t="n">
         <v>0.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J9" t="n">
         <v>0.02</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37836,11 +37836,11 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -37850,23 +37850,25 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
       <c r="G10" t="n">
-        <v>0.327</v>
+        <v>0.34</v>
       </c>
       <c r="H10" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L10" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="11">
@@ -37876,11 +37878,11 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -37890,26 +37892,24 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="G11" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02</v>
+        <v>0.044</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.019</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -37918,11 +37918,11 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -37932,21 +37932,23 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.455</v>
+        <v>0.44</v>
       </c>
       <c r="G12" t="n">
-        <v>0.334</v>
+        <v>0.33</v>
       </c>
       <c r="H12" t="n">
-        <v>0.053</v>
+        <v>0.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L12" t="n">
         <v>0.02</v>
       </c>
@@ -37962,7 +37964,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -37972,26 +37974,24 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="G13" t="n">
-        <v>0.31</v>
+        <v>0.334</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="I13" t="n">
-        <v>0.11</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38000,11 +38000,11 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -38017,19 +38017,19 @@
         <v>0.46</v>
       </c>
       <c r="G14" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J14" t="n">
         <v>0.03</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L14" t="n">
         <v>0.01</v>
@@ -38042,11 +38042,11 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -38056,25 +38056,25 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="G15" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H15" t="n">
         <v>0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -38084,11 +38084,11 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -38098,23 +38098,25 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="G16" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J16" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L16" t="n">
-        <v>0.014</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17">
@@ -38124,11 +38126,11 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -38138,22 +38140,22 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.48</v>
+        <v>0.448</v>
       </c>
       <c r="G17" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.06</v>
+        <v>0.114</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -38164,11 +38166,11 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -38178,25 +38180,23 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="G18" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="H18" t="n">
         <v>0.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K18" t="n">
         <v>0.02</v>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19">
@@ -38206,11 +38206,11 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -38220,22 +38220,22 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.445</v>
+        <v>0.45</v>
       </c>
       <c r="G19" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H19" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="J19" t="n">
         <v>0.03</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L19" t="n">
         <v>0.02</v>
@@ -38252,7 +38252,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -38262,23 +38262,25 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="G20" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="I20" t="n">
-        <v>0.115</v>
+        <v>0.125</v>
       </c>
       <c r="J20" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L20" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21">
@@ -38288,11 +38290,11 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -38302,26 +38304,24 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.45</v>
+        <v>0.446</v>
       </c>
       <c r="G21" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08</v>
+        <v>0.115</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.011</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -38330,11 +38330,11 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -38344,16 +38344,16 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="G22" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H22" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="J22" t="n">
         <v>0.02</v>
@@ -38361,7 +38361,9 @@
       <c r="K22" t="n">
         <v>0.01</v>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -38370,11 +38372,11 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46130</v>
+        <v>46132</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -38384,25 +38386,23 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="G23" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H23" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K23" t="n">
         <v>0.02</v>
       </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="24">
@@ -38412,11 +38412,11 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -38426,23 +38426,25 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.458</v>
+        <v>0.45</v>
       </c>
       <c r="G24" t="n">
-        <v>0.315</v>
+        <v>0.33</v>
       </c>
       <c r="H24" t="n">
-        <v>0.053</v>
+        <v>0.06</v>
       </c>
       <c r="I24" t="n">
-        <v>0.119</v>
+        <v>0.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L24" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="25">
@@ -38452,11 +38454,11 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>April 13, 2026</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -38465,12 +38467,24 @@
       <c r="E25" t="b">
         <v>0</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.009000000000000001</v>
+      </c>
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -38480,11 +38494,11 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46123</v>
+        <v>46125</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>April 13, 2026</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -38493,27 +38507,13 @@
       <c r="E26" t="b">
         <v>0</v>
       </c>
-      <c r="F26" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -38522,11 +38522,11 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -38536,23 +38536,25 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.453</v>
+        <v>0.43</v>
       </c>
       <c r="G27" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H27" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.122</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L27" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="28">
@@ -38562,11 +38564,11 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -38576,20 +38578,22 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.46</v>
+        <v>0.453</v>
       </c>
       <c r="G28" t="n">
         <v>0.32</v>
       </c>
       <c r="H28" t="n">
-        <v>0.06</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>0.122</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.035</v>
+      </c>
       <c r="K28" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -38604,7 +38608,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -38614,25 +38618,21 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G29" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H29" t="n">
         <v>0.06</v>
       </c>
       <c r="I29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
         <v>0.08</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="30">
@@ -38642,11 +38642,11 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -38656,25 +38656,25 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G30" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J30" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="31">
@@ -38684,11 +38684,11 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46116</v>
+        <v>46119</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -38698,25 +38698,25 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="G31" t="n">
         <v>0.33</v>
       </c>
       <c r="H31" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>0.09</v>
       </c>
       <c r="J31" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K31" t="n">
         <v>0.02</v>
       </c>
       <c r="L31" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -38726,11 +38726,11 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -38740,23 +38740,25 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.457</v>
+        <v>0.44</v>
       </c>
       <c r="G32" t="n">
-        <v>0.305</v>
+        <v>0.33</v>
       </c>
       <c r="H32" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I32" t="n">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="J32" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L32" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="33">
@@ -38766,11 +38768,11 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -38780,22 +38782,22 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.48</v>
+        <v>0.457</v>
       </c>
       <c r="G33" t="n">
-        <v>0.34</v>
+        <v>0.305</v>
       </c>
       <c r="H33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>0.06</v>
+        <v>0.125</v>
       </c>
       <c r="J33" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="L33" t="inlineStr"/>
     </row>
@@ -38806,11 +38808,11 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>March 29, 2026</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -38819,13 +38821,25 @@
       <c r="E34" t="b">
         <v>0</v>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.03</v>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -38834,11 +38848,11 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>March 29, 2026</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -38847,27 +38861,13 @@
       <c r="E35" t="b">
         <v>0</v>
       </c>
-      <c r="F35" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -38876,11 +38876,11 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -38890,23 +38890,25 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.465</v>
+        <v>0.45</v>
       </c>
       <c r="G36" t="n">
-        <v>0.322</v>
+        <v>0.33</v>
       </c>
       <c r="H36" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.113</v>
+        <v>0.09</v>
       </c>
       <c r="J36" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L36" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="37">
@@ -38916,11 +38918,11 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -38930,20 +38932,22 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.46</v>
+        <v>0.465</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3</v>
+        <v>0.322</v>
       </c>
       <c r="H37" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="I37" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>0.113</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.036</v>
+      </c>
       <c r="K37" t="n">
-        <v>0.08</v>
+        <v>0.011</v>
       </c>
       <c r="L37" t="inlineStr"/>
     </row>
@@ -38954,11 +38958,11 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -38968,25 +38972,21 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G38" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H38" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
+        <v>0.11</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="39">
@@ -38996,11 +38996,11 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46102</v>
+        <v>46105</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -39010,13 +39010,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G39" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H39" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I39" t="n">
         <v>0.09</v>
@@ -39025,10 +39025,10 @@
         <v>0.03</v>
       </c>
       <c r="K39" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L39" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -39038,11 +39038,11 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -39052,23 +39052,25 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.457</v>
+        <v>0.46</v>
       </c>
       <c r="G40" t="n">
-        <v>0.329</v>
+        <v>0.32</v>
       </c>
       <c r="H40" t="n">
-        <v>0.048</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>0.115</v>
+        <v>0.09</v>
       </c>
       <c r="J40" t="n">
-        <v>0.03700000000000001</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L40" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="41">
@@ -39078,11 +39080,11 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -39092,22 +39094,22 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.44</v>
+        <v>0.457</v>
       </c>
       <c r="G41" t="n">
-        <v>0.36</v>
+        <v>0.329</v>
       </c>
       <c r="H41" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="I41" t="n">
-        <v>0.09</v>
+        <v>0.115</v>
       </c>
       <c r="J41" t="n">
-        <v>0.02</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="L41" t="inlineStr"/>
     </row>
@@ -39118,11 +39120,11 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>46096</v>
+        <v>46098</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -39132,25 +39134,23 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.475</v>
+        <v>0.44</v>
       </c>
       <c r="G42" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>0.151</v>
+        <v>0.09</v>
       </c>
       <c r="J42" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="43">
@@ -39160,11 +39160,11 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -39174,25 +39174,25 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.45</v>
+        <v>0.475</v>
       </c>
       <c r="G43" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="H43" t="n">
-        <v>0.06</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.08</v>
+        <v>0.151</v>
       </c>
       <c r="J43" t="n">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
       <c r="K43" t="n">
-        <v>0.04</v>
+        <v>0.015</v>
       </c>
       <c r="L43" t="n">
-        <v>0.04</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="44">
@@ -39202,11 +39202,11 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -39216,23 +39216,25 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.478</v>
+        <v>0.45</v>
       </c>
       <c r="G44" t="n">
-        <v>0.311</v>
+        <v>0.31</v>
       </c>
       <c r="H44" t="n">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
       <c r="I44" t="n">
-        <v>0.112</v>
+        <v>0.08</v>
       </c>
       <c r="J44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K44" t="n">
         <v>0.04</v>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>0.011</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="45">
@@ -39242,11 +39244,11 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -39256,26 +39258,24 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.46</v>
+        <v>0.478</v>
       </c>
       <c r="G45" t="n">
-        <v>0.35</v>
+        <v>0.311</v>
       </c>
       <c r="H45" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="I45" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="J45" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.011</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -39284,11 +39284,11 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46088</v>
+        <v>46092</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -39298,25 +39298,25 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H46" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J46" t="n">
         <v>0.03</v>
       </c>
       <c r="K46" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L46" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -39326,11 +39326,11 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -39340,22 +39340,26 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G47" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H47" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.03</v>
+      </c>
       <c r="K47" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -39368,7 +39372,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -39381,20 +39385,18 @@
         <v>0.46</v>
       </c>
       <c r="G48" t="n">
-        <v>0.325</v>
+        <v>0.31</v>
       </c>
       <c r="H48" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="I48" t="n">
         <v>0.1</v>
       </c>
-      <c r="J48" t="n">
-        <v>0.047</v>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="49">
@@ -39404,11 +39406,11 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -39421,23 +39423,21 @@
         <v>0.46</v>
       </c>
       <c r="G49" t="n">
-        <v>0.36</v>
+        <v>0.325</v>
       </c>
       <c r="H49" t="n">
-        <v>0.04</v>
+        <v>0.052</v>
       </c>
       <c r="I49" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02</v>
+        <v>0.047</v>
       </c>
       <c r="K49" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -39450,7 +39450,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -39460,24 +39460,26 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="G50" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H50" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K50" t="n">
         <v>0.03</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>0.02</v>
       </c>
-      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -39486,11 +39488,11 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>46081</v>
+        <v>46083</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -39500,23 +39502,21 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="G51" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H51" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I51" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="J51" t="n">
         <v>0.03</v>
       </c>
-      <c r="K51" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
         <v>0.02</v>
       </c>
@@ -39528,11 +39528,11 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -39542,23 +39542,25 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.436</v>
+        <v>0.43</v>
       </c>
       <c r="G52" t="n">
-        <v>0.332</v>
+        <v>0.33</v>
       </c>
       <c r="H52" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I52" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J52" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L52" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="53">
@@ -39568,11 +39570,11 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -39582,26 +39584,24 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.44</v>
+        <v>0.436</v>
       </c>
       <c r="G53" t="n">
-        <v>0.36</v>
+        <v>0.332</v>
       </c>
       <c r="H53" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="I53" t="n">
-        <v>0.08</v>
+        <v>0.114</v>
       </c>
       <c r="J53" t="n">
-        <v>0.03</v>
+        <v>0.049</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -39610,11 +39610,11 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pollara</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -39624,22 +39624,26 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="G54" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H54" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.03</v>
+      </c>
       <c r="K54" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -39648,11 +39652,11 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Pollara</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -39662,25 +39666,21 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="G55" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="H55" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J55" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="n">
         <v>0.03</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="56">
@@ -39694,7 +39694,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -39704,24 +39704,26 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G56" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H56" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I56" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I56" t="n">
-        <v>0.1</v>
-      </c>
       <c r="J56" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K56" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -39730,11 +39732,11 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>46074</v>
+        <v>46076</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -39747,20 +39749,18 @@
         <v>0.45</v>
       </c>
       <c r="G57" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="H57" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>0.1</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
         <v>0.02</v>
       </c>
@@ -39772,11 +39772,11 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -39786,23 +39786,25 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.413</v>
+        <v>0.45</v>
       </c>
       <c r="G58" t="n">
-        <v>0.337</v>
+        <v>0.33</v>
       </c>
       <c r="H58" t="n">
-        <v>0.076</v>
+        <v>0.06</v>
       </c>
       <c r="I58" t="n">
-        <v>0.106</v>
+        <v>0.1</v>
       </c>
       <c r="J58" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K58" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L58" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="59">
@@ -39812,11 +39814,11 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>46070</v>
+        <v>46073</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -39826,22 +39828,22 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.44</v>
+        <v>0.413</v>
       </c>
       <c r="G59" t="n">
-        <v>0.37</v>
+        <v>0.337</v>
       </c>
       <c r="H59" t="n">
-        <v>0.06</v>
+        <v>0.076</v>
       </c>
       <c r="I59" t="n">
-        <v>0.08</v>
+        <v>0.106</v>
       </c>
       <c r="J59" t="n">
-        <v>0.03</v>
+        <v>0.049</v>
       </c>
       <c r="K59" t="n">
-        <v>0.03</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L59" t="inlineStr"/>
     </row>
@@ -39852,11 +39854,11 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46067</v>
+        <v>46070</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -39866,25 +39868,23 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G60" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="H60" t="n">
         <v>0.06</v>
       </c>
       <c r="I60" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J60" t="n">
         <v>0.03</v>
       </c>
-      <c r="K60" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="61">
@@ -39894,11 +39894,11 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -39908,23 +39908,25 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.381</v>
+        <v>0.43</v>
       </c>
       <c r="G61" t="n">
-        <v>0.365</v>
+        <v>0.34</v>
       </c>
       <c r="H61" t="n">
-        <v>0.083</v>
+        <v>0.06</v>
       </c>
       <c r="I61" t="n">
-        <v>0.111</v>
+        <v>0.09</v>
       </c>
       <c r="J61" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="K61" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L61" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="62">
@@ -39934,11 +39936,11 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>46063</v>
+        <v>46066</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -39948,26 +39950,24 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.44</v>
+        <v>0.381</v>
       </c>
       <c r="G62" t="n">
-        <v>0.37</v>
+        <v>0.365</v>
       </c>
       <c r="H62" t="n">
-        <v>0.06</v>
+        <v>0.083</v>
       </c>
       <c r="I62" t="n">
-        <v>0.08</v>
+        <v>0.111</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03</v>
+        <v>0.044</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -39976,11 +39976,11 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>46060</v>
+        <v>46063</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -39990,25 +39990,25 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="G63" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="H63" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J63" t="n">
         <v>0.03</v>
       </c>
       <c r="K63" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L63" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -40018,11 +40018,11 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -40032,23 +40032,25 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.391</v>
+        <v>0.42</v>
       </c>
       <c r="G64" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="H64" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>0.126</v>
+        <v>0.09</v>
       </c>
       <c r="J64" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="K64" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L64" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="65">
@@ -40058,11 +40060,11 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -40072,26 +40074,24 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.45</v>
+        <v>0.391</v>
       </c>
       <c r="G65" t="n">
-        <v>0.32</v>
+        <v>0.352</v>
       </c>
       <c r="H65" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1</v>
+        <v>0.126</v>
       </c>
       <c r="J65" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="K65" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -40100,11 +40100,11 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -40114,10 +40114,10 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G66" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H66" t="n">
         <v>0.07000000000000001</v>
@@ -40131,7 +40131,9 @@
       <c r="K66" t="n">
         <v>0.02</v>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -40144,7 +40146,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -40154,25 +40156,23 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="G67" t="n">
-        <v>0.355</v>
+        <v>0.38</v>
       </c>
       <c r="H67" t="n">
-        <v>0.055</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="J67" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0.011</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="68">
@@ -40182,11 +40182,11 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>46053</v>
+        <v>46055</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -40196,25 +40196,25 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="G68" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="H68" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I68" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="J68" t="n">
-        <v>0.03</v>
+        <v>0.022</v>
       </c>
       <c r="K68" t="n">
-        <v>0.02</v>
+        <v>0.006</v>
       </c>
       <c r="L68" t="n">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="69">
@@ -40224,11 +40224,11 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -40238,25 +40238,25 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.444</v>
+        <v>0.43</v>
       </c>
       <c r="G69" t="n">
-        <v>0.295</v>
+        <v>0.35</v>
       </c>
       <c r="H69" t="n">
-        <v>0.053</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>0.138</v>
+        <v>0.08</v>
       </c>
       <c r="J69" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K69" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="L69" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="70">
@@ -40270,7 +40270,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -40280,23 +40280,25 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.389</v>
+        <v>0.444</v>
       </c>
       <c r="G70" t="n">
-        <v>0.352</v>
+        <v>0.295</v>
       </c>
       <c r="H70" t="n">
-        <v>0.092</v>
+        <v>0.053</v>
       </c>
       <c r="I70" t="n">
-        <v>0.125</v>
+        <v>0.138</v>
       </c>
       <c r="J70" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K70" t="inlineStr"/>
+        <v>0.039</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.016</v>
+      </c>
       <c r="L70" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="71">
@@ -40306,11 +40308,11 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -40320,26 +40322,24 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.43</v>
+        <v>0.389</v>
       </c>
       <c r="G71" t="n">
-        <v>0.39</v>
+        <v>0.352</v>
       </c>
       <c r="H71" t="n">
-        <v>0.06</v>
+        <v>0.092</v>
       </c>
       <c r="I71" t="n">
-        <v>0.08</v>
+        <v>0.125</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="K71" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.013</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -40348,11 +40348,11 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -40362,24 +40362,26 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G72" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H72" t="n">
         <v>0.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="J72" t="n">
         <v>0.02</v>
       </c>
       <c r="K72" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L72" t="n">
         <v>0.01</v>
       </c>
-      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -40392,7 +40394,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -40402,24 +40404,24 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="G73" t="n">
         <v>0.38</v>
       </c>
       <c r="H73" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J73" t="n">
         <v>0.02</v>
       </c>
-      <c r="K73" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -40428,11 +40430,11 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -40442,23 +40444,21 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="G74" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H74" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I74" t="n">
         <v>0.1</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K74" t="n">
         <v>0.02</v>
       </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
         <v>0.02</v>
       </c>
@@ -40470,11 +40470,11 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -40484,23 +40484,25 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.392</v>
+        <v>0.42</v>
       </c>
       <c r="G75" t="n">
-        <v>0.352</v>
+        <v>0.34</v>
       </c>
       <c r="H75" t="n">
         <v>0.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="K75" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L75" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="76">
@@ -40510,11 +40512,11 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>46039</v>
+        <v>46045</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -40524,26 +40526,24 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.4</v>
+        <v>0.392</v>
       </c>
       <c r="G76" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="H76" t="n">
         <v>0.08</v>
       </c>
       <c r="I76" t="n">
-        <v>0.11</v>
+        <v>0.116</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.021</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -40552,11 +40552,11 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -40566,16 +40566,16 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G77" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="H77" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I77" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J77" t="n">
         <v>0.03</v>
@@ -40598,7 +40598,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -40608,23 +40608,25 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.388</v>
+        <v>0.41</v>
       </c>
       <c r="G78" t="n">
-        <v>0.348</v>
+        <v>0.39</v>
       </c>
       <c r="H78" t="n">
-        <v>0.077</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>0.115</v>
+        <v>0.08</v>
       </c>
       <c r="J78" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="K78" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L78" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="79">
@@ -40634,11 +40636,11 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -40648,26 +40650,24 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4</v>
+        <v>0.388</v>
       </c>
       <c r="G79" t="n">
-        <v>0.4</v>
+        <v>0.348</v>
       </c>
       <c r="H79" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="I79" t="n">
-        <v>0.08</v>
+        <v>0.115</v>
       </c>
       <c r="J79" t="n">
-        <v>0.03</v>
+        <v>0.046</v>
       </c>
       <c r="K79" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.024</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -40676,11 +40676,11 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -40693,21 +40693,23 @@
         <v>0.4</v>
       </c>
       <c r="G80" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H80" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J80" t="n">
         <v>0.03</v>
       </c>
       <c r="K80" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L80" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -40716,11 +40718,11 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>46032</v>
+        <v>46034</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -40730,25 +40732,23 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="G81" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H81" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J81" t="n">
         <v>0.03</v>
       </c>
-      <c r="K81" t="n">
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="n">
         <v>0.02</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="82">
@@ -40758,11 +40758,11 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -40772,23 +40772,25 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.388</v>
+        <v>0.39</v>
       </c>
       <c r="G82" t="n">
-        <v>0.355</v>
+        <v>0.36</v>
       </c>
       <c r="H82" t="n">
-        <v>0.076</v>
+        <v>0.08</v>
       </c>
       <c r="I82" t="n">
-        <v>0.109</v>
+        <v>0.12</v>
       </c>
       <c r="J82" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="K82" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L82" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="83">
@@ -40798,11 +40800,11 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>46025</v>
+        <v>46031</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -40812,26 +40814,24 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.38</v>
+        <v>0.388</v>
       </c>
       <c r="G83" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="H83" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I83" t="n">
-        <v>0.12</v>
+        <v>0.109</v>
       </c>
       <c r="J83" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K83" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.021</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -40840,11 +40840,11 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -40854,23 +40854,25 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="G84" t="n">
-        <v>0.355</v>
+        <v>0.37</v>
       </c>
       <c r="H84" t="n">
-        <v>0.076</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="J84" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="K84" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L84" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="85">
@@ -40880,11 +40882,11 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>46019</v>
+        <v>46024</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -40894,26 +40896,24 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.39</v>
+        <v>0.377</v>
       </c>
       <c r="G85" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="H85" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I85" t="n">
-        <v>0.11</v>
+        <v>0.117</v>
       </c>
       <c r="J85" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K85" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.019</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -40922,11 +40922,11 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>46017</v>
+        <v>46019</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -40936,23 +40936,25 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.384</v>
+        <v>0.39</v>
       </c>
       <c r="G86" t="n">
-        <v>0.347</v>
+        <v>0.37</v>
       </c>
       <c r="H86" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="J86" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="K86" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L86" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="87">
@@ -40962,11 +40964,11 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>46012</v>
+        <v>46017</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -40976,26 +40978,24 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.38</v>
+        <v>0.384</v>
       </c>
       <c r="G87" t="n">
-        <v>0.38</v>
+        <v>0.347</v>
       </c>
       <c r="H87" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>0.12</v>
+        <v>0.113</v>
       </c>
       <c r="J87" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K87" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.017</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -41004,11 +41004,11 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>46010</v>
+        <v>46012</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -41018,23 +41018,25 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.363</v>
+        <v>0.38</v>
       </c>
       <c r="G88" t="n">
-        <v>0.356</v>
+        <v>0.38</v>
       </c>
       <c r="H88" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>0.114</v>
+        <v>0.12</v>
       </c>
       <c r="J88" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K88" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L88" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="89">
@@ -41044,11 +41046,11 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -41058,22 +41060,22 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.409</v>
+        <v>0.363</v>
       </c>
       <c r="G89" t="n">
-        <v>0.377</v>
+        <v>0.356</v>
       </c>
       <c r="H89" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>0.079</v>
+        <v>0.114</v>
       </c>
       <c r="J89" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="K89" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="L89" t="inlineStr"/>
     </row>
@@ -41088,7 +41090,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -41098,23 +41100,23 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4</v>
+        <v>0.409</v>
       </c>
       <c r="G90" t="n">
-        <v>0.37</v>
+        <v>0.377</v>
       </c>
       <c r="H90" t="n">
-        <v>0.09</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="I90" t="n">
-        <v>0.09</v>
+        <v>0.079</v>
       </c>
       <c r="J90" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="91">
@@ -41124,11 +41126,11 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -41138,19 +41140,19 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="G91" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="H91" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J91" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="K91" t="n">
         <v>0.02</v>
@@ -41164,11 +41166,11 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>46003</v>
+        <v>46005</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -41178,25 +41180,23 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G92" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="H92" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I92" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="J92" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="93">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -41220,23 +41220,25 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.385</v>
+        <v>0.41</v>
       </c>
       <c r="G93" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H93" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>0.108</v>
+        <v>0.06</v>
       </c>
       <c r="J93" t="n">
-        <v>0.03700000000000001</v>
-      </c>
-      <c r="K93" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L93" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="94">
@@ -41246,11 +41248,11 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -41260,26 +41262,24 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.41</v>
+        <v>0.385</v>
       </c>
       <c r="G94" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="H94" t="n">
-        <v>0.06</v>
+        <v>0.067</v>
       </c>
       <c r="I94" t="n">
-        <v>0.09</v>
+        <v>0.108</v>
       </c>
       <c r="J94" t="n">
-        <v>0.02</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.019</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -41288,11 +41288,11 @@
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -41302,23 +41302,25 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.391</v>
+        <v>0.41</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="H95" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="J95" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="K95" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L95" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -41328,11 +41330,11 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -41342,22 +41344,22 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="G96" t="n">
-        <v>0.38</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>0.08</v>
+        <v>0.063</v>
       </c>
       <c r="I96" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="J96" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="K96" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="L96" t="inlineStr"/>
     </row>
@@ -41372,7 +41374,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -41382,25 +41384,23 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G97" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="H97" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J97" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="n">
         <v>0.02</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="98">
@@ -41414,7 +41414,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -41424,22 +41424,26 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="G98" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H98" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -41448,11 +41452,11 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -41462,23 +41466,21 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="G99" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H99" t="n">
         <v>0.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J99" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
@@ -41492,7 +41494,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -41502,25 +41504,23 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="G100" t="n">
         <v>0.36</v>
       </c>
       <c r="H100" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="I100" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K100" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="n">
         <v>0.01</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="101">
@@ -41530,11 +41530,11 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>45989</v>
+        <v>45991</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -41544,25 +41544,25 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="G101" t="n">
-        <v>0.382</v>
+        <v>0.36</v>
       </c>
       <c r="H101" t="n">
-        <v>0.073</v>
+        <v>0.05</v>
       </c>
       <c r="I101" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J101" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="K101" t="n">
-        <v>0.003</v>
+        <v>0.02</v>
       </c>
       <c r="L101" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="102">
@@ -41572,11 +41572,11 @@
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -41586,25 +41586,25 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.41</v>
+        <v>0.419</v>
       </c>
       <c r="G102" t="n">
-        <v>0.4</v>
+        <v>0.382</v>
       </c>
       <c r="H102" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="I102" t="n">
-        <v>0.08</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="K102" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="L102" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="103">
@@ -41614,11 +41614,11 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>45982</v>
+        <v>45988</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -41628,25 +41628,25 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H103" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>0.091</v>
+        <v>0.08</v>
       </c>
       <c r="J103" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="K103" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="L103" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="104">
@@ -41656,11 +41656,11 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>45979</v>
+        <v>45982</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kolosowski Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -41670,25 +41670,25 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0.44</v>
+        <v>0.419</v>
       </c>
       <c r="G104" t="n">
-        <v>0.44</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="H104" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>0.03</v>
+        <v>0.091</v>
       </c>
       <c r="J104" t="n">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="L104" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="105">
@@ -41698,11 +41698,11 @@
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Kolosowski Strategies</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -41712,25 +41712,25 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0.402</v>
+        <v>0.44</v>
       </c>
       <c r="G105" t="n">
-        <v>0.382</v>
+        <v>0.44</v>
       </c>
       <c r="H105" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I105" t="n">
-        <v>0.101</v>
+        <v>0.03</v>
       </c>
       <c r="J105" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="K105" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="L105" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -41740,11 +41740,11 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>45972</v>
+        <v>45975</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -41754,25 +41754,25 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.441</v>
+        <v>0.402</v>
       </c>
       <c r="G106" t="n">
-        <v>0.332</v>
+        <v>0.382</v>
       </c>
       <c r="H106" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>0.107</v>
+        <v>0.101</v>
       </c>
       <c r="J106" t="n">
-        <v>0.033</v>
+        <v>0.022</v>
       </c>
       <c r="K106" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="L106" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="107">
@@ -41782,11 +41782,11 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>45969</v>
+        <v>45972</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -41796,25 +41796,25 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="G107" t="n">
-        <v>0.4</v>
+        <v>0.332</v>
       </c>
       <c r="H107" t="n">
-        <v>0.06</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>0.05</v>
+        <v>0.107</v>
       </c>
       <c r="J107" t="n">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="K107" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="L107" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="108">
@@ -41828,7 +41828,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -41841,22 +41841,22 @@
         <v>0.44</v>
       </c>
       <c r="G108" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H108" t="n">
         <v>0.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J108" t="n">
         <v>0.02</v>
       </c>
       <c r="K108" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L108" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="109">
@@ -41866,11 +41866,11 @@
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -41880,22 +41880,26 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="G109" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="H109" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I109" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J109" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -41908,7 +41912,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -41921,23 +41925,19 @@
         <v>0.4</v>
       </c>
       <c r="G110" t="n">
-        <v>0.368</v>
+        <v>0.38</v>
       </c>
       <c r="H110" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="I110" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J110" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L110" t="n">
-        <v>0.012</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -41946,11 +41946,11 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -41963,22 +41963,22 @@
         <v>0.4</v>
       </c>
       <c r="G111" t="n">
-        <v>0.41</v>
+        <v>0.368</v>
       </c>
       <c r="H111" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="I111" t="n">
-        <v>0.08</v>
+        <v>0.114</v>
       </c>
       <c r="J111" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="L111" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="112">
@@ -41988,11 +41988,11 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -42002,25 +42002,25 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0.434</v>
+        <v>0.4</v>
       </c>
       <c r="G112" t="n">
-        <v>0.355</v>
+        <v>0.41</v>
       </c>
       <c r="H112" t="n">
-        <v>0.058</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I112" t="n">
         <v>0.08</v>
       </c>
       <c r="J112" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="K112" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L112" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -42034,7 +42034,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -42044,25 +42044,25 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.42</v>
+        <v>0.434</v>
       </c>
       <c r="G113" t="n">
-        <v>0.38</v>
+        <v>0.355</v>
       </c>
       <c r="H113" t="n">
-        <v>0.05</v>
+        <v>0.058</v>
       </c>
       <c r="I113" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J113" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="K113" t="n">
         <v>0.02</v>
       </c>
-      <c r="K113" t="n">
-        <v>0.01</v>
-      </c>
       <c r="L113" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="114">
@@ -42072,11 +42072,11 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -42086,24 +42086,26 @@
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G114" t="n">
         <v>0.38</v>
       </c>
       <c r="H114" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J114" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="K114" t="n">
         <v>0.01</v>
       </c>
-      <c r="L114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -42112,11 +42114,11 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -42126,25 +42128,23 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0.393</v>
+        <v>0.43</v>
       </c>
       <c r="G115" t="n">
-        <v>0.371</v>
+        <v>0.38</v>
       </c>
       <c r="H115" t="n">
-        <v>0.066</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>0.125</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J115" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="116">
@@ -42154,11 +42154,11 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -42168,25 +42168,25 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="G116" t="n">
-        <v>0.42</v>
+        <v>0.371</v>
       </c>
       <c r="H116" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="I116" t="n">
-        <v>0.08</v>
+        <v>0.125</v>
       </c>
       <c r="J116" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="K116" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="L116" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -42196,11 +42196,11 @@
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>45954</v>
+        <v>45959</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -42210,25 +42210,25 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>0.394</v>
+        <v>0.4</v>
       </c>
       <c r="G117" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H117" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I117" t="n">
-        <v>0.127</v>
+        <v>0.08</v>
       </c>
       <c r="J117" t="n">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L117" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="118">
@@ -42242,7 +42242,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -42252,25 +42252,25 @@
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>0.435</v>
+        <v>0.394</v>
       </c>
       <c r="G118" t="n">
-        <v>0.324</v>
+        <v>0.37</v>
       </c>
       <c r="H118" t="n">
-        <v>0.057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I118" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="J118" t="n">
-        <v>0.03</v>
+        <v>0.016</v>
       </c>
       <c r="K118" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="L118" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -42280,11 +42280,11 @@
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>45947</v>
+        <v>45954</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -42294,25 +42294,25 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0.393</v>
+        <v>0.435</v>
       </c>
       <c r="G119" t="n">
-        <v>0.366</v>
+        <v>0.324</v>
       </c>
       <c r="H119" t="n">
-        <v>0.068</v>
+        <v>0.057</v>
       </c>
       <c r="I119" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="J119" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="K119" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="L119" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="120">
@@ -42322,11 +42322,11 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -42336,25 +42336,25 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="G120" t="n">
-        <v>0.41</v>
+        <v>0.366</v>
       </c>
       <c r="H120" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="I120" t="n">
-        <v>0.08</v>
+        <v>0.121</v>
       </c>
       <c r="J120" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="K120" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="L120" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="121">
@@ -42368,7 +42368,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -42378,25 +42378,25 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G121" t="n">
         <v>0.41</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.37</v>
-      </c>
       <c r="H121" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J121" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L121" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="122">
@@ -42406,11 +42406,11 @@
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -42420,25 +42420,25 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>0.385</v>
+        <v>0.41</v>
       </c>
       <c r="G122" t="n">
-        <v>0.368</v>
+        <v>0.37</v>
       </c>
       <c r="H122" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="I122" t="n">
-        <v>0.122</v>
+        <v>0.11</v>
       </c>
       <c r="J122" t="n">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="K122" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="L122" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -42448,11 +42448,11 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>45935</v>
+        <v>45940</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -42462,24 +42462,26 @@
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>0.44</v>
+        <v>0.385</v>
       </c>
       <c r="G123" t="n">
-        <v>0.38</v>
+        <v>0.368</v>
       </c>
       <c r="H123" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="I123" t="n">
-        <v>0.06</v>
+        <v>0.122</v>
       </c>
       <c r="J123" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K123" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L123" t="inlineStr"/>
+        <v>0.014</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.006999999999999999</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -42488,11 +42490,11 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>45933</v>
+        <v>45935</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -42502,25 +42504,23 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>0.391</v>
+        <v>0.44</v>
       </c>
       <c r="G124" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="H124" t="n">
-        <v>0.062</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>0.115</v>
+        <v>0.06</v>
       </c>
       <c r="J124" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="125">
@@ -42530,11 +42530,11 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -42544,25 +42544,25 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0.4</v>
+        <v>0.391</v>
       </c>
       <c r="G125" t="n">
-        <v>0.41</v>
+        <v>0.379</v>
       </c>
       <c r="H125" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="I125" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.115</v>
       </c>
       <c r="J125" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K125" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L125" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="126">
@@ -42572,11 +42572,11 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>45926</v>
+        <v>45931</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -42586,25 +42586,25 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0.407</v>
+        <v>0.4</v>
       </c>
       <c r="G126" t="n">
-        <v>0.366</v>
+        <v>0.41</v>
       </c>
       <c r="H126" t="n">
-        <v>0.048</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>0.119</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>0.043</v>
+        <v>0.03</v>
       </c>
       <c r="K126" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="L126" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="127">
@@ -42614,11 +42614,11 @@
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -42628,25 +42628,25 @@
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.38</v>
+        <v>0.407</v>
       </c>
       <c r="G127" t="n">
-        <v>0.41</v>
+        <v>0.366</v>
       </c>
       <c r="H127" t="n">
-        <v>0.08</v>
+        <v>0.048</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1</v>
+        <v>0.119</v>
       </c>
       <c r="J127" t="n">
-        <v>0.02</v>
+        <v>0.043</v>
       </c>
       <c r="K127" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="L127" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="128">
@@ -42656,11 +42656,11 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>45921</v>
+        <v>45922</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -42670,13 +42670,13 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="G128" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H128" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I128" t="n">
         <v>0.1</v>
@@ -42688,7 +42688,7 @@
         <v>0.01</v>
       </c>
       <c r="L128" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="129">
@@ -42698,11 +42698,11 @@
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>45919</v>
+        <v>45921</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -42712,25 +42712,25 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>0.406</v>
+        <v>0.43</v>
       </c>
       <c r="G129" t="n">
-        <v>0.357</v>
+        <v>0.37</v>
       </c>
       <c r="H129" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="J129" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="K129" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="L129" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="130">
@@ -42740,11 +42740,11 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -42754,25 +42754,25 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4</v>
+        <v>0.357</v>
       </c>
       <c r="H130" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I130" t="n">
-        <v>0.08</v>
+        <v>0.116</v>
       </c>
       <c r="J130" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="K130" t="n">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="L130" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="131">
@@ -42782,11 +42782,11 @@
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>45912</v>
+        <v>45917</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -42796,19 +42796,19 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="G131" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H131" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I131" t="n">
         <v>0.08</v>
       </c>
       <c r="J131" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K131" t="n">
         <v>0.01</v>
@@ -42828,7 +42828,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -42838,25 +42838,25 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0.418</v>
+        <v>0.43</v>
       </c>
       <c r="G132" t="n">
-        <v>0.345</v>
+        <v>0.38</v>
       </c>
       <c r="H132" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="I132" t="n">
-        <v>0.128</v>
+        <v>0.08</v>
       </c>
       <c r="J132" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="K132" t="n">
         <v>0.01</v>
       </c>
       <c r="L132" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="133">
@@ -42870,7 +42870,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -42880,25 +42880,25 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>0.42</v>
+        <v>0.418</v>
       </c>
       <c r="G133" t="n">
-        <v>0.34</v>
+        <v>0.345</v>
       </c>
       <c r="H133" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
       <c r="I133" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="J133" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="K133" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="L133" t="n">
         <v>0.01</v>
-      </c>
-      <c r="L133" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="134">
@@ -42908,11 +42908,11 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -42922,25 +42922,25 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G134" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="H134" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="I134" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.126</v>
       </c>
       <c r="J134" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L134" t="n">
         <v>0.01</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="135">
@@ -42950,11 +42950,11 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -42964,24 +42964,26 @@
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G135" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H135" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J135" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K135" t="n">
         <v>0.02</v>
       </c>
-      <c r="K135" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L135" t="inlineStr"/>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -42990,11 +42992,11 @@
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>45905</v>
+        <v>45907</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -43004,25 +43006,23 @@
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>0.427</v>
+        <v>0.47</v>
       </c>
       <c r="G136" t="n">
-        <v>0.329</v>
+        <v>0.38</v>
       </c>
       <c r="H136" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I136" t="n">
-        <v>0.128</v>
+        <v>0.06</v>
       </c>
       <c r="J136" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0.013</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="137">
@@ -43032,11 +43032,11 @@
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -43046,25 +43046,25 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>0.38</v>
+        <v>0.427</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4</v>
+        <v>0.329</v>
       </c>
       <c r="H137" t="n">
-        <v>0.08</v>
+        <v>0.052</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1</v>
+        <v>0.128</v>
       </c>
       <c r="J137" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="K137" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="L137" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="138">
@@ -43074,11 +43074,11 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>45902</v>
+        <v>45904</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -43088,16 +43088,16 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="G138" t="n">
         <v>0.4</v>
       </c>
       <c r="H138" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I138" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="J138" t="n">
         <v>0.02</v>
@@ -43106,7 +43106,7 @@
         <v>0.01</v>
       </c>
       <c r="L138" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="139">
@@ -43116,11 +43116,11 @@
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -43130,25 +43130,25 @@
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
       <c r="G139" t="n">
-        <v>0.404</v>
+        <v>0.4</v>
       </c>
       <c r="H139" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I139" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J139" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="K139" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="L139" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="140">
@@ -43158,11 +43158,11 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>45898</v>
+        <v>45901</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -43172,25 +43172,25 @@
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>0.433</v>
+        <v>0.423</v>
       </c>
       <c r="G140" t="n">
-        <v>0.324</v>
+        <v>0.404</v>
       </c>
       <c r="H140" t="n">
-        <v>0.062</v>
+        <v>0.05</v>
       </c>
       <c r="I140" t="n">
-        <v>0.127</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>0.029</v>
+        <v>0.012</v>
       </c>
       <c r="K140" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="L140" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="141">
@@ -43200,11 +43200,11 @@
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>45896</v>
+        <v>45898</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -43214,25 +43214,25 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>0.44</v>
+        <v>0.433</v>
       </c>
       <c r="G141" t="n">
-        <v>0.35</v>
+        <v>0.324</v>
       </c>
       <c r="H141" t="n">
-        <v>0.05</v>
+        <v>0.062</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1</v>
+        <v>0.127</v>
       </c>
       <c r="J141" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="K141" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="L141" t="n">
-        <v>0.02</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -43242,11 +43242,11 @@
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>45891</v>
+        <v>45896</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -43256,25 +43256,25 @@
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="G142" t="n">
-        <v>0.342</v>
+        <v>0.35</v>
       </c>
       <c r="H142" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="I142" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="J142" t="n">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="K142" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="L142" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="143">
@@ -43284,11 +43284,11 @@
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>45888</v>
+        <v>45891</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>August 19, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -43297,13 +43297,27 @@
       <c r="E143" t="b">
         <v>0</v>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
+      <c r="F143" t="n">
+        <v>0.4370000000000001</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.008</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -43316,7 +43330,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>August 19, 2025</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -43325,25 +43339,13 @@
       <c r="E144" t="b">
         <v>0</v>
       </c>
-      <c r="F144" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G144" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
-      <c r="L144" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -43352,11 +43354,11 @@
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>August 18, 2025</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -43365,12 +43367,24 @@
       <c r="E145" t="b">
         <v>0</v>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="F145" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
@@ -43380,11 +43394,11 @@
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>45884</v>
+        <v>45887</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>August 18, 2025</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -43393,27 +43407,13 @@
       <c r="E146" t="b">
         <v>0</v>
       </c>
-      <c r="F146" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="I146" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L146" t="n">
-        <v>0.028</v>
-      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -43422,7 +43422,7 @@
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>45877</v>
+        <v>45884</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -43436,25 +43436,25 @@
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>0.448</v>
+        <v>0.444</v>
       </c>
       <c r="G147" t="n">
-        <v>0.319</v>
+        <v>0.324</v>
       </c>
       <c r="H147" t="n">
-        <v>0.061</v>
+        <v>0.049</v>
       </c>
       <c r="I147" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="J147" t="n">
-        <v>0.026</v>
+        <v>0.032</v>
       </c>
       <c r="K147" t="n">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
       <c r="L147" t="n">
-        <v>0.025</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -43468,7 +43468,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -43478,25 +43478,25 @@
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>0.44</v>
+        <v>0.448</v>
       </c>
       <c r="G148" t="n">
-        <v>0.35</v>
+        <v>0.319</v>
       </c>
       <c r="H148" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="I148" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="J148" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="K148" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
       <c r="L148" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="149">
@@ -43506,11 +43506,11 @@
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -43520,23 +43520,25 @@
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G149" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H149" t="n">
         <v>0.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J149" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="K149" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L149" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="150">
@@ -43546,11 +43548,11 @@
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>45873</v>
+        <v>45876</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -43560,22 +43562,22 @@
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="G150" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H150" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="J150" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="K150" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="L150" t="inlineStr"/>
     </row>
@@ -43586,11 +43588,11 @@
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>45870</v>
+        <v>45873</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -43600,24 +43602,24 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="G151" t="n">
-        <v>0.376</v>
+        <v>0.36</v>
       </c>
       <c r="H151" t="n">
-        <v>0.063</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="J151" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="L151" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -43630,7 +43632,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -43640,25 +43642,23 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G152" t="n">
-        <v>0.325</v>
+        <v>0.376</v>
       </c>
       <c r="H152" t="n">
-        <v>0.053</v>
+        <v>0.063</v>
       </c>
       <c r="I152" t="n">
-        <v>0.12</v>
+        <v>0.075</v>
       </c>
       <c r="J152" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.022</v>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="153">
@@ -43668,11 +43668,11 @@
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>45866</v>
+        <v>45870</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -43682,24 +43682,26 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0.41</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="G153" t="n">
-        <v>0.39</v>
+        <v>0.325</v>
       </c>
       <c r="H153" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="I153" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="J153" t="n">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="K153" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -43708,11 +43710,11 @@
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -43722,25 +43724,23 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="G154" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H154" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J154" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="155">
@@ -43754,7 +43754,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -43764,25 +43764,25 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0.436</v>
+        <v>0.43</v>
       </c>
       <c r="G155" t="n">
-        <v>0.335</v>
+        <v>0.36</v>
       </c>
       <c r="H155" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I155" t="n">
-        <v>0.121</v>
+        <v>0.1</v>
       </c>
       <c r="J155" t="n">
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="K155" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="L155" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="156">
@@ -43792,7 +43792,7 @@
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -43806,25 +43806,25 @@
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0.4429999999999999</v>
+        <v>0.436</v>
       </c>
       <c r="G156" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="H156" t="n">
-        <v>0.066</v>
+        <v>0.059</v>
       </c>
       <c r="I156" t="n">
-        <v>0.103</v>
+        <v>0.121</v>
       </c>
       <c r="J156" t="n">
         <v>0.023</v>
       </c>
       <c r="K156" t="n">
-        <v>0.005</v>
+        <v>0.018</v>
       </c>
       <c r="L156" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="157">
@@ -43834,11 +43834,11 @@
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>45853</v>
+        <v>45856</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -43848,25 +43848,25 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0.43</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="G157" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="H157" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="I157" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="J157" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="K157" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L157" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="158">
@@ -43876,11 +43876,11 @@
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>45852</v>
+        <v>45853</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -43890,25 +43890,25 @@
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="G158" t="n">
-        <v>0.305</v>
+        <v>0.4</v>
       </c>
       <c r="H158" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="I158" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K158" t="n">
         <v>0.01</v>
       </c>
       <c r="L158" t="n">
-        <v>0.036</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="159">
@@ -43918,11 +43918,11 @@
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -43932,25 +43932,25 @@
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>0.445</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G159" t="n">
-        <v>0.338</v>
+        <v>0.305</v>
       </c>
       <c r="H159" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="I159" t="n">
-        <v>0.111</v>
+        <v>0.13</v>
       </c>
       <c r="J159" t="n">
-        <v>0.021</v>
+        <v>0.035</v>
       </c>
       <c r="K159" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="L159" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="160">
@@ -43960,11 +43960,11 @@
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>45844</v>
+        <v>45849</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -43974,24 +43974,26 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0.48</v>
+        <v>0.445</v>
       </c>
       <c r="G160" t="n">
-        <v>0.35</v>
+        <v>0.338</v>
       </c>
       <c r="H160" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I160" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.111</v>
       </c>
       <c r="J160" t="n">
-        <v>0.03</v>
+        <v>0.021</v>
       </c>
       <c r="K160" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L160" t="inlineStr"/>
+        <v>0.019</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.006999999999999999</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -44000,11 +44002,11 @@
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>45842</v>
+        <v>45844</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -44014,7 +44016,7 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="G161" t="n">
         <v>0.35</v>
@@ -44023,14 +44025,12 @@
         <v>0.06</v>
       </c>
       <c r="I161" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="n">
         <v>0.01</v>
       </c>
@@ -44046,7 +44046,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -44056,25 +44056,25 @@
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0.451</v>
+        <v>0.46</v>
       </c>
       <c r="G162" t="n">
-        <v>0.326</v>
+        <v>0.35</v>
       </c>
       <c r="H162" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="I162" t="n">
-        <v>0.115</v>
+        <v>0.09</v>
       </c>
       <c r="J162" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="K162" t="n">
         <v>0.01</v>
       </c>
       <c r="L162" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="163">
@@ -44084,11 +44084,11 @@
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>45840</v>
+        <v>45842</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -44098,22 +44098,22 @@
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>0.47</v>
+        <v>0.451</v>
       </c>
       <c r="G163" t="n">
-        <v>0.37</v>
+        <v>0.326</v>
       </c>
       <c r="H163" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="I163" t="n">
-        <v>0.06</v>
+        <v>0.115</v>
       </c>
       <c r="J163" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="K163" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="L163" t="n">
         <v>0.01</v>
@@ -44130,7 +44130,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -44140,25 +44140,25 @@
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="G164" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="H164" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I164" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="J164" t="n">
         <v>0.02</v>
       </c>
       <c r="K164" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L164" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="165">
@@ -44168,11 +44168,11 @@
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -44182,24 +44182,26 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="G165" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H165" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I165" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J165" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K165" t="n">
         <v>0.02</v>
       </c>
-      <c r="L165" t="inlineStr"/>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -44208,11 +44210,11 @@
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -44222,25 +44224,23 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>0.445</v>
+        <v>0.43</v>
       </c>
       <c r="G166" t="n">
-        <v>0.314</v>
+        <v>0.38</v>
       </c>
       <c r="H166" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.128</v>
+        <v>0.08</v>
       </c>
       <c r="J166" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K166" t="n">
-        <v>0.012</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="167">
@@ -44250,11 +44250,11 @@
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -44264,25 +44264,25 @@
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>0.47</v>
+        <v>0.445</v>
       </c>
       <c r="G167" t="n">
-        <v>0.38</v>
+        <v>0.314</v>
       </c>
       <c r="H167" t="n">
-        <v>0.03</v>
+        <v>0.059</v>
       </c>
       <c r="I167" t="n">
-        <v>0.06</v>
+        <v>0.128</v>
       </c>
       <c r="J167" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="K167" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="L167" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="168">
@@ -44292,11 +44292,11 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>45828</v>
+        <v>45834</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -44306,16 +44306,16 @@
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="G168" t="n">
         <v>0.38</v>
       </c>
       <c r="H168" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I168" t="n">
         <v>0.06</v>
-      </c>
-      <c r="I168" t="n">
-        <v>0.11</v>
       </c>
       <c r="J168" t="n">
         <v>0.03</v>
@@ -44324,7 +44324,7 @@
         <v>0.01</v>
       </c>
       <c r="L168" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="169">
@@ -44338,7 +44338,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -44348,25 +44348,25 @@
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>0.452</v>
+        <v>0.42</v>
       </c>
       <c r="G169" t="n">
-        <v>0.308</v>
+        <v>0.38</v>
       </c>
       <c r="H169" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="I169" t="n">
-        <v>0.122</v>
+        <v>0.11</v>
       </c>
       <c r="J169" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="K169" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="L169" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="170">
@@ -44376,11 +44376,11 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -44390,25 +44390,25 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>0.42</v>
+        <v>0.452</v>
       </c>
       <c r="G170" t="n">
-        <v>0.39</v>
+        <v>0.308</v>
       </c>
       <c r="H170" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="I170" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="J170" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="K170" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="L170" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="171">
@@ -44418,11 +44418,11 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>45821</v>
+        <v>45827</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -44432,25 +44432,25 @@
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>0.442</v>
+        <v>0.42</v>
       </c>
       <c r="G171" t="n">
-        <v>0.322</v>
+        <v>0.39</v>
       </c>
       <c r="H171" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.114</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J171" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="K171" t="n">
         <v>0.01</v>
       </c>
       <c r="L171" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="172">
@@ -44460,11 +44460,11 @@
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>45814</v>
+        <v>45821</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -44474,22 +44474,22 @@
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>0.42</v>
+        <v>0.442</v>
       </c>
       <c r="G172" t="n">
-        <v>0.39</v>
+        <v>0.322</v>
       </c>
       <c r="H172" t="n">
-        <v>0.06</v>
+        <v>0.063</v>
       </c>
       <c r="I172" t="n">
-        <v>0.09</v>
+        <v>0.114</v>
       </c>
       <c r="J172" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
       <c r="K172" t="n">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="L172" t="n">
         <v>0.01</v>
@@ -44506,7 +44506,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -44516,25 +44516,25 @@
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>0.426</v>
+        <v>0.42</v>
       </c>
       <c r="G173" t="n">
-        <v>0.328</v>
+        <v>0.39</v>
       </c>
       <c r="H173" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="J173" t="n">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="K173" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="L173" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="174">
@@ -44544,11 +44544,11 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -44558,25 +44558,25 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>0.42</v>
+        <v>0.426</v>
       </c>
       <c r="G174" t="n">
-        <v>0.39</v>
+        <v>0.328</v>
       </c>
       <c r="H174" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="I174" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="J174" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K174" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="L174" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -44586,11 +44586,11 @@
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>45812</v>
+        <v>45813</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -44600,16 +44600,16 @@
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>0.439</v>
+        <v>0.42</v>
       </c>
       <c r="G175" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="H175" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.127</v>
+        <v>0.08</v>
       </c>
       <c r="J175" t="n">
         <v>0.03</v>
@@ -44618,7 +44618,7 @@
         <v>0.01</v>
       </c>
       <c r="L175" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -44628,11 +44628,11 @@
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>45807</v>
+        <v>45812</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -44642,22 +44642,26 @@
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>0.41</v>
+        <v>0.439</v>
       </c>
       <c r="G176" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="H176" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="I176" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J176" t="inlineStr"/>
+        <v>0.127</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0.03</v>
+      </c>
       <c r="K176" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L176" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -44670,7 +44674,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -44680,25 +44684,21 @@
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>0.417</v>
+        <v>0.41</v>
       </c>
       <c r="G177" t="n">
-        <v>0.364</v>
+        <v>0.4</v>
       </c>
       <c r="H177" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I177" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="J177" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="K177" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="n">
-        <v>0.011</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="178">
@@ -44708,11 +44708,11 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>45800</v>
+        <v>45807</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -44722,25 +44722,25 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>0.44</v>
+        <v>0.417</v>
       </c>
       <c r="G178" t="n">
-        <v>0.39</v>
+        <v>0.364</v>
       </c>
       <c r="H178" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="I178" t="n">
-        <v>0.08</v>
+        <v>0.105</v>
       </c>
       <c r="J178" t="n">
-        <v>0.01</v>
+        <v>0.034</v>
       </c>
       <c r="K178" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="L178" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="179">
@@ -44754,7 +44754,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -44764,25 +44764,25 @@
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>0.404</v>
+        <v>0.44</v>
       </c>
       <c r="G179" t="n">
-        <v>0.386</v>
+        <v>0.39</v>
       </c>
       <c r="H179" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.098</v>
+        <v>0.08</v>
       </c>
       <c r="J179" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="K179" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="L179" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="180">
@@ -44792,11 +44792,11 @@
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -44806,24 +44806,26 @@
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>0.42</v>
+        <v>0.404</v>
       </c>
       <c r="G180" t="n">
-        <v>0.39</v>
+        <v>0.386</v>
       </c>
       <c r="H180" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I180" t="n">
-        <v>0.08</v>
+        <v>0.098</v>
       </c>
       <c r="J180" t="n">
-        <v>0.03</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K180" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L180" t="inlineStr"/>
+        <v>0.013</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -44832,11 +44834,11 @@
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -44846,13 +44848,13 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="G181" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H181" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I181" t="n">
         <v>0.08</v>
@@ -44860,11 +44862,9 @@
       <c r="J181" t="n">
         <v>0.03</v>
       </c>
-      <c r="K181" t="n">
-        <v>0</v>
-      </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="182">
@@ -44874,11 +44874,11 @@
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>45793</v>
+        <v>45798</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -44888,25 +44888,25 @@
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>0.414</v>
+        <v>0.41</v>
       </c>
       <c r="G182" t="n">
-        <v>0.396</v>
+        <v>0.4</v>
       </c>
       <c r="H182" t="n">
-        <v>0.047</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I182" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J182" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K182" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="L182" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -44916,11 +44916,11 @@
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>45786</v>
+        <v>45793</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -44930,25 +44930,25 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>0.45</v>
+        <v>0.414</v>
       </c>
       <c r="G183" t="n">
-        <v>0.4</v>
+        <v>0.396</v>
       </c>
       <c r="H183" t="n">
-        <v>0.06</v>
+        <v>0.047</v>
       </c>
       <c r="I183" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="K183" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="L183" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="184">
@@ -44962,7 +44962,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -44972,25 +44972,25 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0.415</v>
+        <v>0.45</v>
       </c>
       <c r="G184" t="n">
-        <v>0.405</v>
+        <v>0.4</v>
       </c>
       <c r="H184" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.078</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>0.033</v>
+        <v>0.01</v>
       </c>
       <c r="K184" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="L184" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -45000,11 +45000,11 @@
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>45782</v>
+        <v>45786</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>May 5, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -45013,13 +45013,27 @@
       <c r="E185" t="b">
         <v>0</v>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
+      <c r="F185" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -45028,11 +45042,11 @@
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>45779</v>
+        <v>45782</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>May 5, 2025</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -45041,27 +45055,13 @@
       <c r="E186" t="b">
         <v>0</v>
       </c>
-      <c r="F186" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="G186" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="H186" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="I186" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="J186" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K186" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L186" t="n">
-        <v>0.013</v>
-      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -45070,11 +45070,11 @@
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>April 30, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -45083,13 +45083,27 @@
       <c r="E187" t="b">
         <v>0</v>
       </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
+      <c r="F187" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0.008</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -45098,11 +45112,11 @@
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>April 29, 2025</t>
+          <t>April 30, 2025</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -45126,11 +45140,11 @@
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>April 29, 2025</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -45139,40 +45153,26 @@
       <c r="E189" t="b">
         <v>0</v>
       </c>
-      <c r="F189" t="n">
-        <v>0.4379999999999999</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="H189" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="I189" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="J189" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K189" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L189" t="n">
-        <v>0.006999999999999999</v>
-      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Quebec</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>46139</v>
+        <v>45775</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -45182,25 +45182,25 @@
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>0.42</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="G190" t="n">
-        <v>0.21</v>
+        <v>0.413</v>
       </c>
       <c r="H190" t="n">
-        <v>0.22</v>
+        <v>0.063</v>
       </c>
       <c r="I190" t="n">
-        <v>0.09</v>
+        <v>0.063</v>
       </c>
       <c r="J190" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="K190" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="L190" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="191">
@@ -45210,11 +45210,11 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -45224,24 +45224,26 @@
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="G191" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H191" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="I191" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="J191" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K191" t="n">
         <v>0.02</v>
       </c>
-      <c r="K191" t="n">
+      <c r="L191" t="n">
         <v>0.01</v>
       </c>
-      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -45250,7 +45252,7 @@
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>45971</v>
+        <v>46132</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -45264,13 +45266,13 @@
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="G192" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="H192" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="I192" t="n">
         <v>0.05</v>
@@ -45290,7 +45292,7 @@
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>45915</v>
+        <v>45971</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -45304,19 +45306,19 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="G193" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H193" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="I193" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J193" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K193" t="n">
         <v>0.01</v>
@@ -45330,7 +45332,7 @@
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>45887</v>
+        <v>45915</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -45344,24 +45346,24 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G194" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H194" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="I194" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J194" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K194" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -45370,7 +45372,7 @@
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>45830</v>
+        <v>45887</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -45384,24 +45386,24 @@
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G195" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="H195" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="I195" t="n">
         <v>0.05</v>
       </c>
       <c r="J195" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -45410,11 +45412,11 @@
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>45775</v>
+        <v>45830</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -45424,39 +45426,37 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0.426</v>
+        <v>0.44</v>
       </c>
       <c r="G196" t="n">
-        <v>0.233</v>
+        <v>0.23</v>
       </c>
       <c r="H196" t="n">
-        <v>0.277</v>
+        <v>0.25</v>
       </c>
       <c r="I196" t="n">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="J196" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="K196" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Quebec</t>
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>45802</v>
+        <v>45775</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -45466,22 +45466,26 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>0.54</v>
+        <v>0.426</v>
       </c>
       <c r="G197" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H197" t="inlineStr"/>
+        <v>0.233</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.277</v>
+      </c>
       <c r="I197" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="J197" t="n">
-        <v>0.03</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="K197" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L197" t="inlineStr"/>
+        <v>0.008</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -45490,11 +45494,11 @@
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>45775</v>
+        <v>45802</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -45504,37 +45508,35 @@
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="G198" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="J198" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K198" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Manitoba</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>46094</v>
+        <v>45775</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Probe Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -45544,20 +45546,24 @@
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="G199" t="n">
-        <v>0.39</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J199" t="inlineStr"/>
+        <v>0.049</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0.012</v>
+      </c>
       <c r="K199" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L199" t="inlineStr"/>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -45566,7 +45572,7 @@
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>46001</v>
+        <v>46094</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -45580,20 +45586,20 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="G200" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -45602,11 +45608,11 @@
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>45775</v>
+        <v>46001</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Probe Research</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -45616,37 +45622,33 @@
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>0.408</v>
+        <v>0.43</v>
       </c>
       <c r="G201" t="n">
-        <v>0.463</v>
+        <v>0.38</v>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J201" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="K201" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Alberta</t>
+          <t>Manitoba</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>46134</v>
+        <v>45775</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -45656,23 +45658,23 @@
         <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>0.403</v>
+        <v>0.408</v>
       </c>
       <c r="G202" t="n">
-        <v>0.458</v>
+        <v>0.463</v>
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J202" t="n">
-        <v>0.011</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="K202" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="L202" t="n">
-        <v>0.025</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="203">
@@ -45682,11 +45684,11 @@
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>46078</v>
+        <v>46134</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -45696,23 +45698,23 @@
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>0.36</v>
+        <v>0.403</v>
       </c>
       <c r="G203" t="n">
-        <v>0.51</v>
+        <v>0.458</v>
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="K203" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="L203" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="204">
@@ -45722,11 +45724,11 @@
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>46065</v>
+        <v>46078</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -45736,23 +45738,23 @@
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="G204" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J204" t="n">
         <v>0.01</v>
       </c>
       <c r="K204" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L204" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="205">
@@ -45762,11 +45764,11 @@
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>45802</v>
+        <v>46065</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -45776,22 +45778,24 @@
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="G205" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
         <v>0.05</v>
       </c>
       <c r="J205" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="K205" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L205" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -45800,11 +45804,11 @@
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>45775</v>
+        <v>45802</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -45814,37 +45818,35 @@
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>0.279</v>
+        <v>0.35</v>
       </c>
       <c r="G206" t="n">
-        <v>0.635</v>
+        <v>0.54</v>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>0.063</v>
+        <v>0.05</v>
       </c>
       <c r="J206" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="K206" t="n">
-        <v>0.008</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>British Columbia</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>46125</v>
+        <v>45775</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -45854,23 +45856,23 @@
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>0.512</v>
+        <v>0.279</v>
       </c>
       <c r="G207" t="n">
-        <v>0.322</v>
+        <v>0.635</v>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="J207" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.004</v>
       </c>
       <c r="K207" t="n">
-        <v>0.032</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="208">
@@ -45880,7 +45882,7 @@
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>46094</v>
+        <v>46125</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -45894,23 +45896,23 @@
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>0.467</v>
+        <v>0.512</v>
       </c>
       <c r="G208" t="n">
-        <v>0.341</v>
+        <v>0.322</v>
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
-        <v>0.096</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="J208" t="n">
-        <v>0.039</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K208" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="L208" t="n">
-        <v>0.014</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="209">
@@ -45920,11 +45922,11 @@
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>45775</v>
+        <v>46094</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -45934,23 +45936,63 @@
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>0.418</v>
+        <v>0.467</v>
       </c>
       <c r="G209" t="n">
-        <v>0.41</v>
+        <v>0.341</v>
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="n">
+        <v>45775</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2025 election</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E210" t="b">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="n">
         <v>0.13</v>
       </c>
-      <c r="J209" t="n">
+      <c r="J210" t="n">
         <v>0.03</v>
       </c>
-      <c r="K209" t="n">
+      <c r="K210" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L210" t="n">
         <v>0.006</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0.005</v>
       </c>
     </row>
   </sheetData>

--- a/output/preprocessed_data.xlsx
+++ b/output/preprocessed_data.xlsx
@@ -37391,25 +37391,25 @@
         <v>46181</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01465427463960587</v>
+        <v>-0.04360308724446822</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.09765692923147765</v>
+        <v>-0.2010816493041725</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2290216444081314</v>
+        <v>0.5805987841121125</v>
       </c>
       <c r="E2" t="n">
         <v>-0.1293416997003018</v>
       </c>
       <c r="F2" t="n">
-        <v>1.011182327339828</v>
+        <v>3.126981013514841</v>
       </c>
       <c r="G2" t="n">
         <v>-0.3143755756434194</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8083119552969112</v>
+        <v>0.8083312144292495</v>
       </c>
       <c r="I2" t="n">
         <v>0.8000004825507991</v>

--- a/output/preprocessed_data.xlsx
+++ b/output/preprocessed_data.xlsx
@@ -37388,34 +37388,34 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.04581340055687626</v>
+        <v>-0.04581338799834742</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.204191715343619</v>
+        <v>-0.2041916514305028</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5947494301757402</v>
+        <v>0.5947493964530643</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1267672215460279</v>
+        <v>-0.1267672192202733</v>
       </c>
       <c r="F2" t="n">
-        <v>3.160898402154346</v>
+        <v>3.160897382682045</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.301601234657971</v>
+        <v>-0.3016012334216732</v>
       </c>
       <c r="H2" t="n">
-        <v>0.79573907688336</v>
+        <v>0.7957390849491234</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8000004972119215</v>
+        <v>0.8000005021970272</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1999995027880785</v>
+        <v>0.1999994978029728</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -37424,7 +37424,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.972119214557173e-06</v>
+        <v>5.02197027192177e-06</v>
       </c>
     </row>
   </sheetData>
@@ -37510,11 +37510,11 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -37524,24 +37524,26 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.423</v>
+        <v>0.4</v>
       </c>
       <c r="G2" t="n">
-        <v>0.294</v>
+        <v>0.32</v>
       </c>
       <c r="H2" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.131</v>
+        <v>0.15</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="K2" t="n">
         <v>0.02</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37550,11 +37552,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -37564,26 +37566,24 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4</v>
+        <v>0.423</v>
       </c>
       <c r="G3" t="n">
-        <v>0.32</v>
+        <v>0.294</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="I3" t="n">
-        <v>0.15</v>
+        <v>0.131</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="K3" t="n">
         <v>0.02</v>
       </c>
-      <c r="L3" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/output/preprocessed_data.xlsx
+++ b/output/preprocessed_data.xlsx
@@ -37388,34 +37388,34 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.04581338799834742</v>
+        <v>-0.04674012611465643</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2041916514305028</v>
+        <v>-0.2014813094893066</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5947493964530643</v>
+        <v>0.589496514008877</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1267672192202733</v>
+        <v>-0.1249296454626644</v>
       </c>
       <c r="F2" t="n">
-        <v>3.160897382682045</v>
+        <v>3.163463194782735</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3016012334216732</v>
+        <v>-0.3137222082729709</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7957390849491234</v>
+        <v>0.7898396011446795</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8000005021970272</v>
+        <v>0.800000507231984</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1999994978029728</v>
+        <v>0.199999492768016</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -37424,7 +37424,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.02197027192177e-06</v>
+        <v>5.072319839860012e-06</v>
       </c>
     </row>
   </sheetData>
@@ -37438,7 +37438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L212"/>
+  <dimension ref="A1:L213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37494,12 +37494,12 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>oth</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>ppc</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>oth</t>
         </is>
       </c>
     </row>
@@ -37510,11 +37510,11 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46179</v>
+        <v>46183</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -37524,26 +37524,24 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="G2" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="H2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37552,11 +37550,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -37566,24 +37564,26 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.423</v>
+        <v>0.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.294</v>
+        <v>0.32</v>
       </c>
       <c r="H3" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.131</v>
+        <v>0.15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="K3" t="n">
         <v>0.02</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37592,11 +37592,11 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -37606,25 +37606,23 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="G4" t="n">
-        <v>0.36</v>
+        <v>0.294</v>
       </c>
       <c r="H4" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.06</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="5">
@@ -37634,11 +37632,11 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -37648,21 +37646,23 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="G5" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H5" t="n">
         <v>0.06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" t="n">
         <v>0.01</v>
       </c>
@@ -37674,11 +37674,11 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -37688,26 +37688,24 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H6" t="n">
         <v>0.06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="J6" t="n">
         <v>0.02</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37716,11 +37714,11 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -37730,24 +37728,26 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.403</v>
+        <v>0.41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.328</v>
+        <v>0.32</v>
       </c>
       <c r="H7" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.132</v>
+        <v>0.16</v>
       </c>
       <c r="J7" t="n">
-        <v>0.051</v>
+        <v>0.02</v>
       </c>
       <c r="K7" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37756,11 +37756,11 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46166</v>
+        <v>46171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -37770,23 +37770,23 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.45</v>
+        <v>0.403</v>
       </c>
       <c r="G8" t="n">
-        <v>0.32</v>
+        <v>0.328</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>0.132</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03</v>
+        <v>0.051</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="9">
@@ -37796,11 +37796,11 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -37810,26 +37810,24 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="G9" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>0.11</v>
       </c>
       <c r="J9" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.02</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37838,11 +37836,11 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -37852,24 +37850,26 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.411</v>
+        <v>0.43</v>
       </c>
       <c r="G10" t="n">
-        <v>0.327</v>
+        <v>0.31</v>
       </c>
       <c r="H10" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.126</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>0.048</v>
+        <v>0.02</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -37878,11 +37878,11 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -37892,24 +37892,24 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.47</v>
+        <v>0.411</v>
       </c>
       <c r="G11" t="n">
-        <v>0.35</v>
+        <v>0.327</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08</v>
+        <v>0.126</v>
       </c>
       <c r="J11" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
         <v>0.02</v>
       </c>
-      <c r="K11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -37918,11 +37918,11 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46158</v>
+        <v>46162</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -37932,25 +37932,23 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="G12" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="H12" t="n">
         <v>0.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
         <v>0.02</v>
       </c>
-      <c r="K12" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="13">
@@ -37960,11 +37958,11 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -37974,24 +37972,26 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.327</v>
+        <v>0.34</v>
       </c>
       <c r="H13" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>0.044</v>
+        <v>0.02</v>
       </c>
       <c r="K13" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38000,11 +38000,11 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -38014,25 +38014,23 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="G14" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.044</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="15">
@@ -38042,11 +38040,11 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -38056,24 +38054,26 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.455</v>
+        <v>0.44</v>
       </c>
       <c r="G15" t="n">
-        <v>0.334</v>
+        <v>0.33</v>
       </c>
       <c r="H15" t="n">
-        <v>0.053</v>
+        <v>0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="K15" t="n">
         <v>0.02</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -38086,7 +38086,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -38096,25 +38096,23 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="G16" t="n">
-        <v>0.31</v>
+        <v>0.334</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="I16" t="n">
-        <v>0.11</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.035</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17">
@@ -38124,11 +38122,11 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -38141,13 +38139,13 @@
         <v>0.46</v>
       </c>
       <c r="G17" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J17" t="n">
         <v>0.03</v>
@@ -38156,7 +38154,7 @@
         <v>0.01</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18">
@@ -38166,11 +38164,11 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -38180,25 +38178,25 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="G18" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H18" t="n">
         <v>0.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19">
@@ -38208,11 +38206,11 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -38222,24 +38220,26 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="G19" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H19" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J19" t="n">
-        <v>0.034</v>
+        <v>0.02</v>
       </c>
       <c r="K19" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -38248,11 +38248,11 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -38262,23 +38262,23 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.48</v>
+        <v>0.448</v>
       </c>
       <c r="G20" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="H20" t="n">
-        <v>0.06</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06</v>
+        <v>0.114</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="21">
@@ -38288,11 +38288,11 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -38302,26 +38302,24 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="G21" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="H21" t="n">
         <v>0.06</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="J21" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -38330,11 +38328,11 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -38344,16 +38342,16 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.445</v>
+        <v>0.45</v>
       </c>
       <c r="G22" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H22" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="J22" t="n">
         <v>0.03</v>
@@ -38362,7 +38360,7 @@
         <v>0.02</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="23">
@@ -38376,7 +38374,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -38386,24 +38384,26 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="G23" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H23" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="I23" t="n">
-        <v>0.115</v>
+        <v>0.125</v>
       </c>
       <c r="J23" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K23" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -38412,11 +38412,11 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -38426,25 +38426,23 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.45</v>
+        <v>0.446</v>
       </c>
       <c r="G24" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="H24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.08</v>
+        <v>0.115</v>
       </c>
       <c r="J24" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.035</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="25">
@@ -38454,11 +38452,11 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -38468,21 +38466,23 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="G25" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H25" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="J25" t="n">
         <v>0.02</v>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L25" t="n">
         <v>0.01</v>
       </c>
@@ -38494,11 +38494,11 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46130</v>
+        <v>46132</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -38508,26 +38508,24 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="G26" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H26" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J26" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -38536,11 +38534,11 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -38550,24 +38548,26 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.458</v>
+        <v>0.45</v>
       </c>
       <c r="G27" t="n">
-        <v>0.315</v>
+        <v>0.33</v>
       </c>
       <c r="H27" t="n">
-        <v>0.053</v>
+        <v>0.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.119</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K27" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -38576,11 +38576,11 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>April 13, 2026</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -38589,13 +38589,25 @@
       <c r="E28" t="b">
         <v>0</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.035</v>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0.009000000000000001</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -38604,11 +38616,11 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>46123</v>
+        <v>46125</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>April 13, 2026</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -38617,27 +38629,13 @@
       <c r="E29" t="b">
         <v>0</v>
       </c>
-      <c r="F29" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -38646,11 +38644,11 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -38660,24 +38658,26 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.453</v>
+        <v>0.43</v>
       </c>
       <c r="G30" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H30" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>0.122</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -38686,11 +38686,11 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -38700,21 +38700,23 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.46</v>
+        <v>0.453</v>
       </c>
       <c r="G31" t="n">
         <v>0.32</v>
       </c>
       <c r="H31" t="n">
-        <v>0.06</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>0.122</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.035</v>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32">
@@ -38728,7 +38730,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -38738,26 +38740,22 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G32" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H32" t="n">
         <v>0.06</v>
       </c>
       <c r="I32" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
         <v>0.08</v>
       </c>
-      <c r="J32" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -38766,11 +38764,11 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -38780,25 +38778,25 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G33" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K33" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="34">
@@ -38808,11 +38806,11 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46116</v>
+        <v>46119</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -38822,22 +38820,22 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="G34" t="n">
         <v>0.33</v>
       </c>
       <c r="H34" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I34" t="n">
         <v>0.09</v>
       </c>
       <c r="J34" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K34" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0.02</v>
@@ -38850,11 +38848,11 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -38864,24 +38862,26 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.457</v>
+        <v>0.44</v>
       </c>
       <c r="G35" t="n">
-        <v>0.305</v>
+        <v>0.33</v>
       </c>
       <c r="H35" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="J35" t="n">
-        <v>0.042</v>
+        <v>0.03</v>
       </c>
       <c r="K35" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -38890,11 +38890,11 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -38904,23 +38904,23 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.48</v>
+        <v>0.457</v>
       </c>
       <c r="G36" t="n">
-        <v>0.34</v>
+        <v>0.305</v>
       </c>
       <c r="H36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>0.06</v>
+        <v>0.125</v>
       </c>
       <c r="J36" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="37">
@@ -38930,11 +38930,11 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>March 29, 2026</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -38943,12 +38943,24 @@
       <c r="E37" t="b">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -38958,11 +38970,11 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>March 29, 2026</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -38971,27 +38983,13 @@
       <c r="E38" t="b">
         <v>0</v>
       </c>
-      <c r="F38" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -39000,11 +38998,11 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -39014,24 +39012,26 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.465</v>
+        <v>0.45</v>
       </c>
       <c r="G39" t="n">
-        <v>0.322</v>
+        <v>0.33</v>
       </c>
       <c r="H39" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.113</v>
+        <v>0.09</v>
       </c>
       <c r="J39" t="n">
-        <v>0.036</v>
+        <v>0.02</v>
       </c>
       <c r="K39" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -39040,11 +39040,11 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -39054,21 +39054,23 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.46</v>
+        <v>0.465</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3</v>
+        <v>0.322</v>
       </c>
       <c r="H40" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="I40" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J40" t="inlineStr"/>
+        <v>0.113</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.036</v>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>0.08</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="41">
@@ -39078,11 +39080,11 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -39092,26 +39094,22 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G41" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H41" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I41" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.11</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -39120,11 +39118,11 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>46102</v>
+        <v>46105</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -39134,13 +39132,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G42" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I42" t="n">
         <v>0.09</v>
@@ -39149,10 +39147,10 @@
         <v>0.03</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="43">
@@ -39162,11 +39160,11 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -39176,24 +39174,26 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.457</v>
+        <v>0.46</v>
       </c>
       <c r="G43" t="n">
-        <v>0.329</v>
+        <v>0.32</v>
       </c>
       <c r="H43" t="n">
-        <v>0.048</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.115</v>
+        <v>0.09</v>
       </c>
       <c r="J43" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="K43" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -39202,11 +39202,11 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -39216,23 +39216,23 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.44</v>
+        <v>0.457</v>
       </c>
       <c r="G44" t="n">
-        <v>0.36</v>
+        <v>0.329</v>
       </c>
       <c r="H44" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="I44" t="n">
-        <v>0.09</v>
+        <v>0.115</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="45">
@@ -39242,11 +39242,11 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>46096</v>
+        <v>46098</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -39256,26 +39256,24 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.475</v>
+        <v>0.44</v>
       </c>
       <c r="G45" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H45" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>0.151</v>
+        <v>0.09</v>
       </c>
       <c r="J45" t="n">
-        <v>0.045</v>
+        <v>0.02</v>
       </c>
       <c r="K45" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -39284,11 +39282,11 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -39298,25 +39296,25 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.45</v>
+        <v>0.475</v>
       </c>
       <c r="G46" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="H46" t="n">
-        <v>0.06</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.08</v>
+        <v>0.151</v>
       </c>
       <c r="J46" t="n">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
       <c r="K46" t="n">
-        <v>0.04</v>
+        <v>0.004</v>
       </c>
       <c r="L46" t="n">
-        <v>0.04</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="47">
@@ -39326,11 +39324,11 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -39340,24 +39338,26 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.478</v>
+        <v>0.45</v>
       </c>
       <c r="G47" t="n">
-        <v>0.311</v>
+        <v>0.31</v>
       </c>
       <c r="H47" t="n">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.112</v>
+        <v>0.08</v>
       </c>
       <c r="J47" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K47" t="n">
         <v>0.04</v>
       </c>
-      <c r="K47" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -39366,11 +39366,11 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -39380,25 +39380,23 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.46</v>
+        <v>0.478</v>
       </c>
       <c r="G48" t="n">
-        <v>0.35</v>
+        <v>0.311</v>
       </c>
       <c r="H48" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="I48" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="J48" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="49">
@@ -39408,11 +39406,11 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>46088</v>
+        <v>46092</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -39422,25 +39420,25 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H49" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J49" t="n">
         <v>0.03</v>
       </c>
       <c r="K49" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="50">
@@ -39450,11 +39448,11 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -39464,21 +39462,25 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G50" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H50" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.03</v>
+      </c>
       <c r="L50" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="51">
@@ -39492,7 +39494,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -39505,19 +39507,17 @@
         <v>0.46</v>
       </c>
       <c r="G51" t="n">
-        <v>0.325</v>
+        <v>0.31</v>
       </c>
       <c r="H51" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="I51" t="n">
         <v>0.1</v>
       </c>
-      <c r="J51" t="n">
-        <v>0.047</v>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="L51" t="inlineStr"/>
     </row>
@@ -39528,11 +39528,11 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -39545,22 +39545,20 @@
         <v>0.46</v>
       </c>
       <c r="G52" t="n">
-        <v>0.36</v>
+        <v>0.325</v>
       </c>
       <c r="H52" t="n">
-        <v>0.04</v>
+        <v>0.052</v>
       </c>
       <c r="I52" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.047</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>0.02</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -39574,7 +39572,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -39584,23 +39582,25 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="G53" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H53" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I53" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L53" t="n">
         <v>0.03</v>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="54">
@@ -39610,11 +39610,11 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>46081</v>
+        <v>46083</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -39624,16 +39624,16 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="G54" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H54" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I54" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="J54" t="n">
         <v>0.03</v>
@@ -39641,9 +39641,7 @@
       <c r="K54" t="n">
         <v>0.02</v>
       </c>
-      <c r="L54" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -39652,11 +39650,11 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -39666,24 +39664,26 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.436</v>
+        <v>0.43</v>
       </c>
       <c r="G55" t="n">
-        <v>0.332</v>
+        <v>0.33</v>
       </c>
       <c r="H55" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I55" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J55" t="n">
-        <v>0.049</v>
+        <v>0.03</v>
       </c>
       <c r="K55" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -39692,11 +39692,11 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -39706,25 +39706,23 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.44</v>
+        <v>0.436</v>
       </c>
       <c r="G56" t="n">
-        <v>0.36</v>
+        <v>0.332</v>
       </c>
       <c r="H56" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="I56" t="n">
-        <v>0.08</v>
+        <v>0.114</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.049</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -39734,11 +39732,11 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pollara</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -39748,21 +39746,25 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="G57" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H57" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
       <c r="L57" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="58">
@@ -39772,11 +39774,11 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Pollara</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -39786,26 +39788,22 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="G58" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="H58" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J58" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
         <v>0.03</v>
       </c>
-      <c r="K58" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -39818,7 +39816,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -39828,23 +39826,25 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G59" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H59" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I59" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I59" t="n">
-        <v>0.1</v>
-      </c>
       <c r="J59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
       <c r="L59" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="60">
@@ -39854,11 +39854,11 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46074</v>
+        <v>46076</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -39871,23 +39871,21 @@
         <v>0.45</v>
       </c>
       <c r="G60" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="H60" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I60" t="n">
         <v>0.1</v>
       </c>
       <c r="J60" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="K60" t="n">
         <v>0.02</v>
       </c>
-      <c r="L60" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -39896,11 +39894,11 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -39910,24 +39908,26 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.413</v>
+        <v>0.45</v>
       </c>
       <c r="G61" t="n">
-        <v>0.337</v>
+        <v>0.33</v>
       </c>
       <c r="H61" t="n">
-        <v>0.076</v>
+        <v>0.06</v>
       </c>
       <c r="I61" t="n">
-        <v>0.106</v>
+        <v>0.1</v>
       </c>
       <c r="J61" t="n">
-        <v>0.049</v>
+        <v>0.02</v>
       </c>
       <c r="K61" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L61" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -39936,11 +39936,11 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>46070</v>
+        <v>46073</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -39950,23 +39950,23 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.44</v>
+        <v>0.413</v>
       </c>
       <c r="G62" t="n">
-        <v>0.37</v>
+        <v>0.337</v>
       </c>
       <c r="H62" t="n">
-        <v>0.06</v>
+        <v>0.076</v>
       </c>
       <c r="I62" t="n">
-        <v>0.08</v>
+        <v>0.106</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03</v>
+        <v>0.049</v>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>0.03</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -39976,11 +39976,11 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>46067</v>
+        <v>46070</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -39990,26 +39990,24 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G63" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="H63" t="n">
         <v>0.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J63" t="n">
         <v>0.03</v>
       </c>
       <c r="K63" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -40018,11 +40016,11 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -40032,24 +40030,26 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.381</v>
+        <v>0.43</v>
       </c>
       <c r="G64" t="n">
-        <v>0.365</v>
+        <v>0.34</v>
       </c>
       <c r="H64" t="n">
-        <v>0.083</v>
+        <v>0.06</v>
       </c>
       <c r="I64" t="n">
-        <v>0.111</v>
+        <v>0.09</v>
       </c>
       <c r="J64" t="n">
-        <v>0.044</v>
+        <v>0.03</v>
       </c>
       <c r="K64" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -40058,11 +40058,11 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>46063</v>
+        <v>46066</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -40072,25 +40072,23 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.44</v>
+        <v>0.381</v>
       </c>
       <c r="G65" t="n">
-        <v>0.37</v>
+        <v>0.365</v>
       </c>
       <c r="H65" t="n">
-        <v>0.06</v>
+        <v>0.083</v>
       </c>
       <c r="I65" t="n">
-        <v>0.08</v>
+        <v>0.111</v>
       </c>
       <c r="J65" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.044</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -40100,11 +40098,11 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>46060</v>
+        <v>46063</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -40114,25 +40112,25 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="G66" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="H66" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J66" t="n">
         <v>0.03</v>
       </c>
       <c r="K66" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="67">
@@ -40142,11 +40140,11 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -40156,24 +40154,26 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.391</v>
+        <v>0.42</v>
       </c>
       <c r="G67" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="H67" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>0.126</v>
+        <v>0.09</v>
       </c>
       <c r="J67" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="K67" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L67" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -40182,11 +40182,11 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -40196,25 +40196,23 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.45</v>
+        <v>0.391</v>
       </c>
       <c r="G68" t="n">
-        <v>0.32</v>
+        <v>0.352</v>
       </c>
       <c r="H68" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1</v>
+        <v>0.126</v>
       </c>
       <c r="J68" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.029</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -40224,11 +40222,11 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -40238,10 +40236,10 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G69" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H69" t="n">
         <v>0.07000000000000001</v>
@@ -40252,7 +40250,9 @@
       <c r="J69" t="n">
         <v>0.03</v>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L69" t="n">
         <v>0.02</v>
       </c>
@@ -40268,7 +40268,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -40278,26 +40278,24 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="G70" t="n">
-        <v>0.355</v>
+        <v>0.38</v>
       </c>
       <c r="H70" t="n">
-        <v>0.055</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="J70" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
       <c r="K70" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0.011</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -40306,11 +40304,11 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>46053</v>
+        <v>46055</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -40320,25 +40318,25 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="G71" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="H71" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I71" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="J71" t="n">
-        <v>0.03</v>
+        <v>0.022</v>
       </c>
       <c r="K71" t="n">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="L71" t="n">
-        <v>0.02</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="72">
@@ -40348,11 +40346,11 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -40362,25 +40360,25 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.444</v>
+        <v>0.43</v>
       </c>
       <c r="G72" t="n">
-        <v>0.295</v>
+        <v>0.35</v>
       </c>
       <c r="H72" t="n">
-        <v>0.053</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>0.138</v>
+        <v>0.08</v>
       </c>
       <c r="J72" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K72" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="L72" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="73">
@@ -40394,7 +40392,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -40404,24 +40402,26 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.389</v>
+        <v>0.444</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352</v>
+        <v>0.295</v>
       </c>
       <c r="H73" t="n">
-        <v>0.092</v>
+        <v>0.053</v>
       </c>
       <c r="I73" t="n">
-        <v>0.125</v>
+        <v>0.138</v>
       </c>
       <c r="J73" t="n">
-        <v>0.025</v>
+        <v>0.039</v>
       </c>
       <c r="K73" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="L73" t="inlineStr"/>
+        <v>0.015</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.016</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -40430,11 +40430,11 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -40444,25 +40444,23 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.43</v>
+        <v>0.389</v>
       </c>
       <c r="G74" t="n">
-        <v>0.39</v>
+        <v>0.352</v>
       </c>
       <c r="H74" t="n">
-        <v>0.06</v>
+        <v>0.092</v>
       </c>
       <c r="I74" t="n">
-        <v>0.08</v>
+        <v>0.125</v>
       </c>
       <c r="J74" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="75">
@@ -40472,11 +40470,11 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -40486,23 +40484,25 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G75" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H75" t="n">
         <v>0.06</v>
       </c>
       <c r="I75" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="J75" t="n">
         <v>0.02</v>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L75" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="76">
@@ -40516,7 +40516,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -40526,24 +40526,24 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="G76" t="n">
         <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J76" t="n">
         <v>0.02</v>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -40552,11 +40552,11 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -40566,26 +40566,24 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="G77" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H77" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I77" t="n">
         <v>0.1</v>
       </c>
       <c r="J77" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K77" t="n">
         <v>0.02</v>
       </c>
-      <c r="L77" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -40594,11 +40592,11 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -40608,24 +40606,26 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.392</v>
+        <v>0.42</v>
       </c>
       <c r="G78" t="n">
-        <v>0.352</v>
+        <v>0.34</v>
       </c>
       <c r="H78" t="n">
         <v>0.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="J78" t="n">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="K78" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="L78" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -40634,11 +40634,11 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>46039</v>
+        <v>46045</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -40648,25 +40648,23 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4</v>
+        <v>0.392</v>
       </c>
       <c r="G79" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="H79" t="n">
         <v>0.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.11</v>
+        <v>0.116</v>
       </c>
       <c r="J79" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.036</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="80">
@@ -40676,11 +40674,11 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -40690,16 +40688,16 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G80" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="H80" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J80" t="n">
         <v>0.03</v>
@@ -40722,7 +40720,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -40732,24 +40730,26 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.388</v>
+        <v>0.41</v>
       </c>
       <c r="G81" t="n">
-        <v>0.348</v>
+        <v>0.39</v>
       </c>
       <c r="H81" t="n">
-        <v>0.077</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>0.115</v>
+        <v>0.08</v>
       </c>
       <c r="J81" t="n">
-        <v>0.046</v>
+        <v>0.03</v>
       </c>
       <c r="K81" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L81" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -40758,11 +40758,11 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -40772,25 +40772,23 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4</v>
+        <v>0.388</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4</v>
+        <v>0.348</v>
       </c>
       <c r="H82" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="I82" t="n">
-        <v>0.08</v>
+        <v>0.115</v>
       </c>
       <c r="J82" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.046</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="n">
-        <v>0.01</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="83">
@@ -40800,11 +40798,11 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -40817,20 +40815,22 @@
         <v>0.4</v>
       </c>
       <c r="G83" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H83" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J83" t="n">
         <v>0.03</v>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L83" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="84">
@@ -40840,11 +40840,11 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>46032</v>
+        <v>46034</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -40854,26 +40854,24 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="G84" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H84" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J84" t="n">
         <v>0.03</v>
       </c>
       <c r="K84" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L84" t="n">
         <v>0.02</v>
       </c>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -40882,11 +40880,11 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -40896,24 +40894,26 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.388</v>
+        <v>0.39</v>
       </c>
       <c r="G85" t="n">
-        <v>0.355</v>
+        <v>0.36</v>
       </c>
       <c r="H85" t="n">
-        <v>0.076</v>
+        <v>0.08</v>
       </c>
       <c r="I85" t="n">
-        <v>0.109</v>
+        <v>0.12</v>
       </c>
       <c r="J85" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K85" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="L85" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -40922,11 +40922,11 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>46025</v>
+        <v>46031</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -40936,25 +40936,23 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.38</v>
+        <v>0.388</v>
       </c>
       <c r="G86" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="H86" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I86" t="n">
-        <v>0.12</v>
+        <v>0.109</v>
       </c>
       <c r="J86" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.039</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="87">
@@ -40964,11 +40962,11 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -40978,24 +40976,26 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="G87" t="n">
-        <v>0.355</v>
+        <v>0.37</v>
       </c>
       <c r="H87" t="n">
-        <v>0.076</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="J87" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K87" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L87" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -41004,11 +41004,11 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>46019</v>
+        <v>46024</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -41018,25 +41018,23 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.39</v>
+        <v>0.377</v>
       </c>
       <c r="G88" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="H88" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I88" t="n">
-        <v>0.11</v>
+        <v>0.117</v>
       </c>
       <c r="J88" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.039</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="89">
@@ -41046,11 +41044,11 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>46017</v>
+        <v>46019</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -41060,24 +41058,26 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.384</v>
+        <v>0.39</v>
       </c>
       <c r="G89" t="n">
-        <v>0.347</v>
+        <v>0.37</v>
       </c>
       <c r="H89" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="J89" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K89" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="L89" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -41086,11 +41086,11 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>46012</v>
+        <v>46017</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -41100,25 +41100,23 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.38</v>
+        <v>0.384</v>
       </c>
       <c r="G90" t="n">
-        <v>0.38</v>
+        <v>0.347</v>
       </c>
       <c r="H90" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>0.12</v>
+        <v>0.113</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.039</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="91">
@@ -41128,11 +41126,11 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>46010</v>
+        <v>46012</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -41142,24 +41140,26 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.363</v>
+        <v>0.38</v>
       </c>
       <c r="G91" t="n">
-        <v>0.356</v>
+        <v>0.38</v>
       </c>
       <c r="H91" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>0.114</v>
+        <v>0.12</v>
       </c>
       <c r="J91" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K91" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="L91" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -41168,11 +41168,11 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -41182,23 +41182,23 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.409</v>
+        <v>0.363</v>
       </c>
       <c r="G92" t="n">
-        <v>0.377</v>
+        <v>0.356</v>
       </c>
       <c r="H92" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>0.079</v>
+        <v>0.114</v>
       </c>
       <c r="J92" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="93">
@@ -41212,7 +41212,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -41222,22 +41222,22 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4</v>
+        <v>0.409</v>
       </c>
       <c r="G93" t="n">
-        <v>0.37</v>
+        <v>0.377</v>
       </c>
       <c r="H93" t="n">
-        <v>0.09</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="I93" t="n">
-        <v>0.09</v>
+        <v>0.079</v>
       </c>
       <c r="J93" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="K93" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="L93" t="inlineStr"/>
     </row>
@@ -41248,11 +41248,11 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -41262,19 +41262,19 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="G94" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="H94" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J94" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
@@ -41288,11 +41288,11 @@
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>46003</v>
+        <v>46005</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -41302,26 +41302,24 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G95" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="H95" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="J95" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="K95" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -41334,7 +41332,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -41344,24 +41342,26 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.385</v>
+        <v>0.41</v>
       </c>
       <c r="G96" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H96" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>0.108</v>
+        <v>0.06</v>
       </c>
       <c r="J96" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="K96" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L96" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -41370,11 +41370,11 @@
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -41384,25 +41384,23 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.41</v>
+        <v>0.385</v>
       </c>
       <c r="G97" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="H97" t="n">
-        <v>0.06</v>
+        <v>0.067</v>
       </c>
       <c r="I97" t="n">
-        <v>0.09</v>
+        <v>0.108</v>
       </c>
       <c r="J97" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="98">
@@ -41412,11 +41410,11 @@
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -41426,24 +41424,26 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.391</v>
+        <v>0.41</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="H98" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="I98" t="n">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="J98" t="n">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="K98" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="L98" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -41452,11 +41452,11 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -41466,23 +41466,23 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="G99" t="n">
-        <v>0.38</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="H99" t="n">
-        <v>0.08</v>
+        <v>0.063</v>
       </c>
       <c r="I99" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="J99" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="100">
@@ -41496,7 +41496,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -41506,26 +41506,24 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G100" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="H100" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I100" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J100" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K100" t="n">
         <v>0.02</v>
       </c>
-      <c r="K100" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -41538,7 +41536,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -41548,22 +41546,26 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="G101" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H101" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J101" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -41572,11 +41574,11 @@
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -41586,24 +41588,22 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="G102" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H102" t="n">
         <v>0.09</v>
       </c>
       <c r="I102" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J102" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -41616,7 +41616,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -41626,26 +41626,24 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="G103" t="n">
         <v>0.36</v>
       </c>
       <c r="H103" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="I103" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="J103" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="K103" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L103" t="n">
         <v>0.01</v>
       </c>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -41654,11 +41652,11 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>45989</v>
+        <v>45991</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -41668,25 +41666,25 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="G104" t="n">
-        <v>0.382</v>
+        <v>0.36</v>
       </c>
       <c r="H104" t="n">
-        <v>0.073</v>
+        <v>0.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J104" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="K104" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="L104" t="n">
-        <v>0.003</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="105">
@@ -41696,11 +41694,11 @@
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -41710,25 +41708,25 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0.41</v>
+        <v>0.419</v>
       </c>
       <c r="G105" t="n">
-        <v>0.4</v>
+        <v>0.382</v>
       </c>
       <c r="H105" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="I105" t="n">
-        <v>0.08</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="K105" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="L105" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="106">
@@ -41738,11 +41736,11 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>45982</v>
+        <v>45988</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -41752,25 +41750,25 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H106" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>0.091</v>
+        <v>0.08</v>
       </c>
       <c r="J106" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="K106" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="L106" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="107">
@@ -41780,11 +41778,11 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>45979</v>
+        <v>45982</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kolosowski Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -41794,25 +41792,25 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0.44</v>
+        <v>0.419</v>
       </c>
       <c r="G107" t="n">
-        <v>0.44</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="H107" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>0.03</v>
+        <v>0.091</v>
       </c>
       <c r="J107" t="n">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="K107" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="108">
@@ -41822,11 +41820,11 @@
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Kolosowski Strategies</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -41836,25 +41834,25 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>0.402</v>
+        <v>0.44</v>
       </c>
       <c r="G108" t="n">
-        <v>0.382</v>
+        <v>0.44</v>
       </c>
       <c r="H108" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.101</v>
+        <v>0.03</v>
       </c>
       <c r="J108" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="K108" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="109">
@@ -41864,11 +41862,11 @@
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>45972</v>
+        <v>45975</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -41878,25 +41876,25 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.441</v>
+        <v>0.402</v>
       </c>
       <c r="G109" t="n">
-        <v>0.332</v>
+        <v>0.382</v>
       </c>
       <c r="H109" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>0.107</v>
+        <v>0.101</v>
       </c>
       <c r="J109" t="n">
-        <v>0.033</v>
+        <v>0.022</v>
       </c>
       <c r="K109" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="L109" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="110">
@@ -41906,11 +41904,11 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>45969</v>
+        <v>45972</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -41920,25 +41918,25 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="G110" t="n">
-        <v>0.4</v>
+        <v>0.332</v>
       </c>
       <c r="H110" t="n">
-        <v>0.06</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>0.05</v>
+        <v>0.107</v>
       </c>
       <c r="J110" t="n">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="K110" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="L110" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="111">
@@ -41952,7 +41950,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -41965,22 +41963,22 @@
         <v>0.44</v>
       </c>
       <c r="G111" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H111" t="n">
         <v>0.06</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J111" t="n">
         <v>0.02</v>
       </c>
       <c r="K111" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L111" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="112">
@@ -41990,11 +41988,11 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -42004,22 +42002,26 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="G112" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="H112" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J112" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -42032,7 +42034,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -42045,23 +42047,19 @@
         <v>0.4</v>
       </c>
       <c r="G113" t="n">
-        <v>0.368</v>
+        <v>0.38</v>
       </c>
       <c r="H113" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="I113" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J113" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0.008</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -42070,11 +42068,11 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -42087,22 +42085,22 @@
         <v>0.4</v>
       </c>
       <c r="G114" t="n">
-        <v>0.41</v>
+        <v>0.368</v>
       </c>
       <c r="H114" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="I114" t="n">
-        <v>0.08</v>
+        <v>0.114</v>
       </c>
       <c r="J114" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="K114" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="115">
@@ -42112,11 +42110,11 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -42126,25 +42124,25 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0.434</v>
+        <v>0.4</v>
       </c>
       <c r="G115" t="n">
-        <v>0.355</v>
+        <v>0.41</v>
       </c>
       <c r="H115" t="n">
-        <v>0.058</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I115" t="n">
         <v>0.08</v>
       </c>
       <c r="J115" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="K115" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="116">
@@ -42158,7 +42156,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -42168,25 +42166,25 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>0.42</v>
+        <v>0.434</v>
       </c>
       <c r="G116" t="n">
-        <v>0.38</v>
+        <v>0.355</v>
       </c>
       <c r="H116" t="n">
-        <v>0.05</v>
+        <v>0.058</v>
       </c>
       <c r="I116" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J116" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="K116" t="n">
         <v>0.02</v>
       </c>
-      <c r="K116" t="n">
-        <v>0.01</v>
-      </c>
       <c r="L116" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="117">
@@ -42196,11 +42194,11 @@
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -42210,21 +42208,23 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G117" t="n">
         <v>0.38</v>
       </c>
       <c r="H117" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I117" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J117" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K117" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L117" t="n">
         <v>0.01</v>
       </c>
@@ -42236,11 +42236,11 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -42250,26 +42250,24 @@
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>0.393</v>
+        <v>0.43</v>
       </c>
       <c r="G118" t="n">
-        <v>0.371</v>
+        <v>0.38</v>
       </c>
       <c r="H118" t="n">
-        <v>0.066</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I118" t="n">
-        <v>0.125</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>0.017</v>
+        <v>0.04</v>
       </c>
       <c r="K118" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -42278,11 +42276,11 @@
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -42292,25 +42290,25 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="G119" t="n">
-        <v>0.42</v>
+        <v>0.371</v>
       </c>
       <c r="H119" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="I119" t="n">
-        <v>0.08</v>
+        <v>0.125</v>
       </c>
       <c r="J119" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="K119" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="120">
@@ -42320,11 +42318,11 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>45954</v>
+        <v>45959</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -42334,25 +42332,25 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0.394</v>
+        <v>0.4</v>
       </c>
       <c r="G120" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H120" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I120" t="n">
-        <v>0.127</v>
+        <v>0.08</v>
       </c>
       <c r="J120" t="n">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
       <c r="K120" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="121">
@@ -42366,7 +42364,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -42376,25 +42374,25 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0.435</v>
+        <v>0.394</v>
       </c>
       <c r="G121" t="n">
-        <v>0.324</v>
+        <v>0.37</v>
       </c>
       <c r="H121" t="n">
-        <v>0.057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="J121" t="n">
-        <v>0.03</v>
+        <v>0.016</v>
       </c>
       <c r="K121" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="122">
@@ -42404,11 +42402,11 @@
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>45947</v>
+        <v>45954</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -42418,25 +42416,25 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>0.393</v>
+        <v>0.435</v>
       </c>
       <c r="G122" t="n">
-        <v>0.366</v>
+        <v>0.324</v>
       </c>
       <c r="H122" t="n">
-        <v>0.068</v>
+        <v>0.057</v>
       </c>
       <c r="I122" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="J122" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="K122" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="L122" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="123">
@@ -42446,11 +42444,11 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -42460,25 +42458,25 @@
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="G123" t="n">
-        <v>0.41</v>
+        <v>0.366</v>
       </c>
       <c r="H123" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="I123" t="n">
-        <v>0.08</v>
+        <v>0.121</v>
       </c>
       <c r="J123" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="K123" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="L123" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="124">
@@ -42492,7 +42490,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -42502,25 +42500,25 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G124" t="n">
         <v>0.41</v>
       </c>
-      <c r="G124" t="n">
-        <v>0.37</v>
-      </c>
       <c r="H124" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J124" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K124" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="125">
@@ -42530,11 +42528,11 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -42544,25 +42542,25 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0.385</v>
+        <v>0.41</v>
       </c>
       <c r="G125" t="n">
-        <v>0.368</v>
+        <v>0.37</v>
       </c>
       <c r="H125" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.122</v>
+        <v>0.11</v>
       </c>
       <c r="J125" t="n">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="K125" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="126">
@@ -42572,11 +42570,11 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>45935</v>
+        <v>45940</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -42586,23 +42584,25 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0.44</v>
+        <v>0.385</v>
       </c>
       <c r="G126" t="n">
-        <v>0.38</v>
+        <v>0.368</v>
       </c>
       <c r="H126" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="I126" t="n">
-        <v>0.06</v>
+        <v>0.122</v>
       </c>
       <c r="J126" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K126" t="inlineStr"/>
+        <v>0.039</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.006999999999999999</v>
+      </c>
       <c r="L126" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="127">
@@ -42612,11 +42612,11 @@
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>45933</v>
+        <v>45935</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -42626,26 +42626,24 @@
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.391</v>
+        <v>0.44</v>
       </c>
       <c r="G127" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="H127" t="n">
-        <v>0.062</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I127" t="n">
-        <v>0.115</v>
+        <v>0.06</v>
       </c>
       <c r="J127" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K127" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -42654,11 +42652,11 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -42668,25 +42666,25 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>0.4</v>
+        <v>0.391</v>
       </c>
       <c r="G128" t="n">
-        <v>0.41</v>
+        <v>0.379</v>
       </c>
       <c r="H128" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="I128" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.115</v>
       </c>
       <c r="J128" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K128" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="L128" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -42696,11 +42694,11 @@
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>45926</v>
+        <v>45931</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -42710,25 +42708,25 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>0.407</v>
+        <v>0.4</v>
       </c>
       <c r="G129" t="n">
-        <v>0.366</v>
+        <v>0.41</v>
       </c>
       <c r="H129" t="n">
-        <v>0.048</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I129" t="n">
-        <v>0.119</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>0.043</v>
+        <v>0.03</v>
       </c>
       <c r="K129" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="L129" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="130">
@@ -42738,11 +42736,11 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -42752,25 +42750,25 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0.38</v>
+        <v>0.407</v>
       </c>
       <c r="G130" t="n">
-        <v>0.41</v>
+        <v>0.366</v>
       </c>
       <c r="H130" t="n">
-        <v>0.08</v>
+        <v>0.048</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1</v>
+        <v>0.119</v>
       </c>
       <c r="J130" t="n">
-        <v>0.02</v>
+        <v>0.043</v>
       </c>
       <c r="K130" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L130" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="131">
@@ -42780,11 +42778,11 @@
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>45921</v>
+        <v>45922</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -42794,13 +42792,13 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="G131" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H131" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I131" t="n">
         <v>0.1</v>
@@ -42809,7 +42807,7 @@
         <v>0.02</v>
       </c>
       <c r="K131" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L131" t="n">
         <v>0.01</v>
@@ -42822,11 +42820,11 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>45919</v>
+        <v>45921</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -42836,25 +42834,25 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0.406</v>
+        <v>0.43</v>
       </c>
       <c r="G132" t="n">
-        <v>0.357</v>
+        <v>0.37</v>
       </c>
       <c r="H132" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="I132" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="J132" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="K132" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="L132" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="133">
@@ -42864,11 +42862,11 @@
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -42878,25 +42876,25 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="G133" t="n">
-        <v>0.4</v>
+        <v>0.357</v>
       </c>
       <c r="H133" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I133" t="n">
-        <v>0.08</v>
+        <v>0.116</v>
       </c>
       <c r="J133" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="K133" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="L133" t="n">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="134">
@@ -42906,11 +42904,11 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>45912</v>
+        <v>45917</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -42920,19 +42918,19 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="G134" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H134" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I134" t="n">
         <v>0.08</v>
       </c>
       <c r="J134" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K134" t="n">
         <v>0.01</v>
@@ -42952,7 +42950,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -42962,22 +42960,22 @@
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>0.418</v>
+        <v>0.43</v>
       </c>
       <c r="G135" t="n">
-        <v>0.345</v>
+        <v>0.38</v>
       </c>
       <c r="H135" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.128</v>
+        <v>0.08</v>
       </c>
       <c r="J135" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="K135" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="L135" t="n">
         <v>0.01</v>
@@ -42994,7 +42992,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -43004,25 +43002,25 @@
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>0.42</v>
+        <v>0.418</v>
       </c>
       <c r="G136" t="n">
-        <v>0.34</v>
+        <v>0.345</v>
       </c>
       <c r="H136" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
       <c r="I136" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="J136" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="K136" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L136" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="137">
@@ -43032,11 +43030,11 @@
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -43046,25 +43044,25 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G137" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="H137" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="I137" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.126</v>
       </c>
       <c r="J137" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K137" t="n">
         <v>0.01</v>
       </c>
-      <c r="K137" t="n">
+      <c r="L137" t="n">
         <v>0.02</v>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -43074,11 +43072,11 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -43088,23 +43086,25 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G138" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H138" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I138" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J138" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
         <v>0.02</v>
-      </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="139">
@@ -43114,11 +43114,11 @@
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>45905</v>
+        <v>45907</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -43128,26 +43128,24 @@
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>0.427</v>
+        <v>0.47</v>
       </c>
       <c r="G139" t="n">
-        <v>0.329</v>
+        <v>0.38</v>
       </c>
       <c r="H139" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I139" t="n">
-        <v>0.128</v>
+        <v>0.06</v>
       </c>
       <c r="J139" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="K139" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="L139" t="n">
-        <v>0.013</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -43156,11 +43154,11 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -43170,25 +43168,25 @@
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>0.38</v>
+        <v>0.427</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4</v>
+        <v>0.329</v>
       </c>
       <c r="H140" t="n">
-        <v>0.08</v>
+        <v>0.052</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1</v>
+        <v>0.128</v>
       </c>
       <c r="J140" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="K140" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="L140" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="141">
@@ -43198,11 +43196,11 @@
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>45902</v>
+        <v>45904</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -43212,22 +43210,22 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="G141" t="n">
         <v>0.4</v>
       </c>
       <c r="H141" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I141" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="J141" t="n">
         <v>0.02</v>
       </c>
       <c r="K141" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L141" t="n">
         <v>0.01</v>
@@ -43240,11 +43238,11 @@
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -43254,25 +43252,25 @@
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
       <c r="G142" t="n">
-        <v>0.404</v>
+        <v>0.4</v>
       </c>
       <c r="H142" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I142" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J142" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="K142" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="L142" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="143">
@@ -43282,11 +43280,11 @@
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>45898</v>
+        <v>45901</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -43296,25 +43294,25 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>0.433</v>
+        <v>0.423</v>
       </c>
       <c r="G143" t="n">
-        <v>0.324</v>
+        <v>0.404</v>
       </c>
       <c r="H143" t="n">
-        <v>0.062</v>
+        <v>0.05</v>
       </c>
       <c r="I143" t="n">
-        <v>0.127</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>0.029</v>
+        <v>0.012</v>
       </c>
       <c r="K143" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L143" t="n">
         <v>0.016</v>
-      </c>
-      <c r="L143" t="n">
-        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="144">
@@ -43324,11 +43322,11 @@
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>45896</v>
+        <v>45898</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -43338,25 +43336,25 @@
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>0.44</v>
+        <v>0.433</v>
       </c>
       <c r="G144" t="n">
-        <v>0.35</v>
+        <v>0.324</v>
       </c>
       <c r="H144" t="n">
-        <v>0.05</v>
+        <v>0.062</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1</v>
+        <v>0.127</v>
       </c>
       <c r="J144" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="K144" t="n">
-        <v>0.02</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L144" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="145">
@@ -43366,11 +43364,11 @@
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>45891</v>
+        <v>45896</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -43380,25 +43378,25 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="G145" t="n">
-        <v>0.342</v>
+        <v>0.35</v>
       </c>
       <c r="H145" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="I145" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="J145" t="n">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="K145" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="L145" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="146">
@@ -43408,11 +43406,11 @@
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>45888</v>
+        <v>45891</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>August 19, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -43421,13 +43419,27 @@
       <c r="E146" t="b">
         <v>0</v>
       </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
+      <c r="F146" t="n">
+        <v>0.4370000000000001</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.016</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -43440,7 +43452,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>August 19, 2025</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -43449,24 +43461,12 @@
       <c r="E147" t="b">
         <v>0</v>
       </c>
-      <c r="F147" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I147" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J147" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
@@ -43476,11 +43476,11 @@
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>August 18, 2025</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -43489,13 +43489,25 @@
       <c r="E148" t="b">
         <v>0</v>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="F148" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0.02</v>
+      </c>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -43504,11 +43516,11 @@
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>45884</v>
+        <v>45887</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>August 18, 2025</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -43517,27 +43529,13 @@
       <c r="E149" t="b">
         <v>0</v>
       </c>
-      <c r="F149" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="I149" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="J149" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="L149" t="n">
-        <v>0.006999999999999999</v>
-      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -43546,7 +43544,7 @@
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>45877</v>
+        <v>45884</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -43560,25 +43558,25 @@
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>0.448</v>
+        <v>0.444</v>
       </c>
       <c r="G150" t="n">
-        <v>0.319</v>
+        <v>0.324</v>
       </c>
       <c r="H150" t="n">
-        <v>0.061</v>
+        <v>0.049</v>
       </c>
       <c r="I150" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="J150" t="n">
-        <v>0.026</v>
+        <v>0.032</v>
       </c>
       <c r="K150" t="n">
-        <v>0.025</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="L150" t="n">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="151">
@@ -43592,7 +43590,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -43602,25 +43600,25 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>0.44</v>
+        <v>0.448</v>
       </c>
       <c r="G151" t="n">
-        <v>0.35</v>
+        <v>0.319</v>
       </c>
       <c r="H151" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="I151" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="J151" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="K151" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="L151" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="152">
@@ -43630,11 +43628,11 @@
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -43644,24 +43642,26 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G152" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H152" t="n">
         <v>0.06</v>
       </c>
       <c r="I152" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J152" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="K152" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L152" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -43670,11 +43670,11 @@
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>45873</v>
+        <v>45876</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -43684,23 +43684,23 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="G153" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H153" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I153" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="J153" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="154">
@@ -43710,11 +43710,11 @@
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>45870</v>
+        <v>45873</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -43724,24 +43724,24 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="G154" t="n">
-        <v>0.376</v>
+        <v>0.36</v>
       </c>
       <c r="H154" t="n">
-        <v>0.063</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I154" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="J154" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="n">
-        <v>0.032</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -43754,7 +43754,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -43764,26 +43764,24 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G155" t="n">
-        <v>0.325</v>
+        <v>0.376</v>
       </c>
       <c r="H155" t="n">
-        <v>0.053</v>
+        <v>0.063</v>
       </c>
       <c r="I155" t="n">
-        <v>0.12</v>
+        <v>0.075</v>
       </c>
       <c r="J155" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="K155" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L155" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.032</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -43792,11 +43790,11 @@
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>45866</v>
+        <v>45870</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -43806,23 +43804,25 @@
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0.41</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>0.39</v>
+        <v>0.325</v>
       </c>
       <c r="H156" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="I156" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="J156" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K156" t="inlineStr"/>
+        <v>0.025</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L156" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="157">
@@ -43832,11 +43832,11 @@
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -43846,26 +43846,24 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="G157" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H157" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J157" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K157" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L157" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -43878,7 +43876,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -43888,25 +43886,25 @@
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0.436</v>
+        <v>0.43</v>
       </c>
       <c r="G158" t="n">
-        <v>0.335</v>
+        <v>0.36</v>
       </c>
       <c r="H158" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I158" t="n">
-        <v>0.121</v>
+        <v>0.1</v>
       </c>
       <c r="J158" t="n">
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="K158" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="L158" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="159">
@@ -43916,7 +43914,7 @@
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -43930,25 +43928,25 @@
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>0.4429999999999999</v>
+        <v>0.436</v>
       </c>
       <c r="G159" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="H159" t="n">
-        <v>0.066</v>
+        <v>0.059</v>
       </c>
       <c r="I159" t="n">
-        <v>0.103</v>
+        <v>0.121</v>
       </c>
       <c r="J159" t="n">
         <v>0.023</v>
       </c>
       <c r="K159" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
       <c r="L159" t="n">
-        <v>0.005</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="160">
@@ -43958,11 +43956,11 @@
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>45853</v>
+        <v>45856</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -43972,25 +43970,25 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0.43</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="G160" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="H160" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="I160" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="J160" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="K160" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L160" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="161">
@@ -44000,11 +43998,11 @@
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>45852</v>
+        <v>45853</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -44014,22 +44012,22 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="G161" t="n">
-        <v>0.305</v>
+        <v>0.4</v>
       </c>
       <c r="H161" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="I161" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K161" t="n">
-        <v>0.036</v>
+        <v>0.01</v>
       </c>
       <c r="L161" t="n">
         <v>0.01</v>
@@ -44042,11 +44040,11 @@
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -44056,25 +44054,25 @@
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0.445</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G162" t="n">
-        <v>0.338</v>
+        <v>0.305</v>
       </c>
       <c r="H162" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="I162" t="n">
-        <v>0.111</v>
+        <v>0.13</v>
       </c>
       <c r="J162" t="n">
-        <v>0.021</v>
+        <v>0.035</v>
       </c>
       <c r="K162" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="L162" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="163">
@@ -44084,11 +44082,11 @@
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>45844</v>
+        <v>45849</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -44098,23 +44096,25 @@
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>0.48</v>
+        <v>0.445</v>
       </c>
       <c r="G163" t="n">
-        <v>0.35</v>
+        <v>0.338</v>
       </c>
       <c r="H163" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I163" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.111</v>
       </c>
       <c r="J163" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K163" t="inlineStr"/>
+        <v>0.021</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0.006999999999999999</v>
+      </c>
       <c r="L163" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="164">
@@ -44124,11 +44124,11 @@
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>45842</v>
+        <v>45844</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -44138,7 +44138,7 @@
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="G164" t="n">
         <v>0.35</v>
@@ -44147,17 +44147,15 @@
         <v>0.06</v>
       </c>
       <c r="I164" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J164" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K164" t="n">
         <v>0.01</v>
       </c>
-      <c r="L164" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -44170,7 +44168,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -44180,22 +44178,22 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0.451</v>
+        <v>0.46</v>
       </c>
       <c r="G165" t="n">
-        <v>0.326</v>
+        <v>0.35</v>
       </c>
       <c r="H165" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.115</v>
+        <v>0.09</v>
       </c>
       <c r="J165" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="K165" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="L165" t="n">
         <v>0.01</v>
@@ -44208,11 +44206,11 @@
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>45840</v>
+        <v>45842</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -44222,25 +44220,25 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>0.47</v>
+        <v>0.451</v>
       </c>
       <c r="G166" t="n">
-        <v>0.37</v>
+        <v>0.326</v>
       </c>
       <c r="H166" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="I166" t="n">
-        <v>0.06</v>
+        <v>0.115</v>
       </c>
       <c r="J166" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="K166" t="n">
         <v>0.01</v>
       </c>
       <c r="L166" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="167">
@@ -44254,7 +44252,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -44264,25 +44262,25 @@
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="G167" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="H167" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I167" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="J167" t="n">
         <v>0.02</v>
       </c>
       <c r="K167" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="168">
@@ -44292,11 +44290,11 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -44306,21 +44304,23 @@
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="G168" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H168" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I168" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J168" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K168" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
       <c r="L168" t="n">
         <v>0.02</v>
       </c>
@@ -44332,11 +44332,11 @@
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -44346,26 +44346,24 @@
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>0.445</v>
+        <v>0.43</v>
       </c>
       <c r="G169" t="n">
-        <v>0.314</v>
+        <v>0.38</v>
       </c>
       <c r="H169" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I169" t="n">
-        <v>0.128</v>
+        <v>0.08</v>
       </c>
       <c r="J169" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="K169" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="L169" t="n">
-        <v>0.012</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -44374,11 +44372,11 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -44388,25 +44386,25 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>0.47</v>
+        <v>0.445</v>
       </c>
       <c r="G170" t="n">
-        <v>0.38</v>
+        <v>0.314</v>
       </c>
       <c r="H170" t="n">
-        <v>0.03</v>
+        <v>0.059</v>
       </c>
       <c r="I170" t="n">
-        <v>0.06</v>
+        <v>0.128</v>
       </c>
       <c r="J170" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="K170" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="L170" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="171">
@@ -44416,11 +44414,11 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>45828</v>
+        <v>45834</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -44430,22 +44428,22 @@
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="G171" t="n">
         <v>0.38</v>
       </c>
       <c r="H171" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I171" t="n">
         <v>0.06</v>
-      </c>
-      <c r="I171" t="n">
-        <v>0.11</v>
       </c>
       <c r="J171" t="n">
         <v>0.03</v>
       </c>
       <c r="K171" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L171" t="n">
         <v>0.01</v>
@@ -44462,7 +44460,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -44472,25 +44470,25 @@
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>0.452</v>
+        <v>0.42</v>
       </c>
       <c r="G172" t="n">
-        <v>0.308</v>
+        <v>0.38</v>
       </c>
       <c r="H172" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="I172" t="n">
-        <v>0.122</v>
+        <v>0.11</v>
       </c>
       <c r="J172" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="K172" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="L172" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="173">
@@ -44500,11 +44498,11 @@
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -44514,25 +44512,25 @@
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>0.42</v>
+        <v>0.452</v>
       </c>
       <c r="G173" t="n">
-        <v>0.39</v>
+        <v>0.308</v>
       </c>
       <c r="H173" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="I173" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="J173" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="K173" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="L173" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="174">
@@ -44542,11 +44540,11 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>45821</v>
+        <v>45827</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -44556,22 +44554,22 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>0.442</v>
+        <v>0.42</v>
       </c>
       <c r="G174" t="n">
-        <v>0.322</v>
+        <v>0.39</v>
       </c>
       <c r="H174" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.114</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="K174" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="L174" t="n">
         <v>0.01</v>
@@ -44584,11 +44582,11 @@
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>45814</v>
+        <v>45821</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -44598,25 +44596,25 @@
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>0.42</v>
+        <v>0.442</v>
       </c>
       <c r="G175" t="n">
-        <v>0.39</v>
+        <v>0.322</v>
       </c>
       <c r="H175" t="n">
-        <v>0.06</v>
+        <v>0.063</v>
       </c>
       <c r="I175" t="n">
-        <v>0.09</v>
+        <v>0.114</v>
       </c>
       <c r="J175" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
       <c r="K175" t="n">
         <v>0.01</v>
       </c>
       <c r="L175" t="n">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="176">
@@ -44630,7 +44628,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -44640,25 +44638,25 @@
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>0.426</v>
+        <v>0.42</v>
       </c>
       <c r="G176" t="n">
-        <v>0.328</v>
+        <v>0.39</v>
       </c>
       <c r="H176" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="I176" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="J176" t="n">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="K176" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="L176" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="177">
@@ -44668,11 +44666,11 @@
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -44682,25 +44680,25 @@
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>0.42</v>
+        <v>0.426</v>
       </c>
       <c r="G177" t="n">
-        <v>0.39</v>
+        <v>0.328</v>
       </c>
       <c r="H177" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="I177" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="J177" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K177" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="178">
@@ -44710,11 +44708,11 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>45812</v>
+        <v>45813</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -44724,22 +44722,22 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>0.439</v>
+        <v>0.42</v>
       </c>
       <c r="G178" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="H178" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I178" t="n">
-        <v>0.127</v>
+        <v>0.08</v>
       </c>
       <c r="J178" t="n">
         <v>0.03</v>
       </c>
       <c r="K178" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="L178" t="n">
         <v>0.01</v>
@@ -44752,11 +44750,11 @@
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>45807</v>
+        <v>45812</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -44766,21 +44764,25 @@
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>0.41</v>
+        <v>0.439</v>
       </c>
       <c r="G179" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="H179" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="I179" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+        <v>0.127</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L179" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="180">
@@ -44794,7 +44796,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -44804,26 +44806,22 @@
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>0.417</v>
+        <v>0.41</v>
       </c>
       <c r="G180" t="n">
-        <v>0.364</v>
+        <v>0.4</v>
       </c>
       <c r="H180" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="J180" t="n">
-        <v>0.034</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="J180" t="inlineStr"/>
       <c r="K180" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L180" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -44832,11 +44830,11 @@
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>45800</v>
+        <v>45807</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -44846,25 +44844,25 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0.44</v>
+        <v>0.417</v>
       </c>
       <c r="G181" t="n">
-        <v>0.39</v>
+        <v>0.364</v>
       </c>
       <c r="H181" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="I181" t="n">
-        <v>0.08</v>
+        <v>0.105</v>
       </c>
       <c r="J181" t="n">
-        <v>0.01</v>
+        <v>0.034</v>
       </c>
       <c r="K181" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="L181" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="182">
@@ -44878,7 +44876,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -44888,25 +44886,25 @@
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>0.404</v>
+        <v>0.44</v>
       </c>
       <c r="G182" t="n">
-        <v>0.386</v>
+        <v>0.39</v>
       </c>
       <c r="H182" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I182" t="n">
-        <v>0.098</v>
+        <v>0.08</v>
       </c>
       <c r="J182" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="K182" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="L182" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="183">
@@ -44916,11 +44914,11 @@
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -44930,23 +44928,25 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>0.42</v>
+        <v>0.404</v>
       </c>
       <c r="G183" t="n">
-        <v>0.39</v>
+        <v>0.386</v>
       </c>
       <c r="H183" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I183" t="n">
-        <v>0.08</v>
+        <v>0.098</v>
       </c>
       <c r="J183" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K183" t="inlineStr"/>
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0.003</v>
+      </c>
       <c r="L183" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="184">
@@ -44956,11 +44956,11 @@
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -44970,13 +44970,13 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="G184" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H184" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I184" t="n">
         <v>0.08</v>
@@ -44985,11 +44985,9 @@
         <v>0.03</v>
       </c>
       <c r="K184" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L184" t="n">
-        <v>0</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -44998,11 +44996,11 @@
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>45793</v>
+        <v>45798</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -45012,25 +45010,25 @@
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>0.414</v>
+        <v>0.41</v>
       </c>
       <c r="G185" t="n">
-        <v>0.396</v>
+        <v>0.4</v>
       </c>
       <c r="H185" t="n">
-        <v>0.047</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J185" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K185" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="186">
@@ -45040,11 +45038,11 @@
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>45786</v>
+        <v>45793</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -45054,25 +45052,25 @@
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>0.45</v>
+        <v>0.414</v>
       </c>
       <c r="G186" t="n">
-        <v>0.4</v>
+        <v>0.396</v>
       </c>
       <c r="H186" t="n">
-        <v>0.06</v>
+        <v>0.047</v>
       </c>
       <c r="I186" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J186" t="n">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="K186" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="187">
@@ -45086,7 +45084,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -45096,25 +45094,25 @@
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>0.415</v>
+        <v>0.45</v>
       </c>
       <c r="G187" t="n">
-        <v>0.405</v>
+        <v>0.4</v>
       </c>
       <c r="H187" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I187" t="n">
-        <v>0.078</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>0.033</v>
+        <v>0.01</v>
       </c>
       <c r="K187" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="188">
@@ -45124,11 +45122,11 @@
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>45782</v>
+        <v>45786</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>May 5, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -45137,13 +45135,27 @@
       <c r="E188" t="b">
         <v>0</v>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
+      <c r="F188" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0.013</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -45152,11 +45164,11 @@
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>45779</v>
+        <v>45782</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>May 5, 2025</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -45165,27 +45177,13 @@
       <c r="E189" t="b">
         <v>0</v>
       </c>
-      <c r="F189" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="H189" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="I189" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="J189" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K189" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="L189" t="n">
-        <v>0.008</v>
-      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -45194,11 +45192,11 @@
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>April 30, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -45207,13 +45205,27 @@
       <c r="E190" t="b">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
+      <c r="F190" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0.013</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -45222,11 +45234,11 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>April 29, 2025</t>
+          <t>April 30, 2025</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -45250,11 +45262,11 @@
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>April 29, 2025</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -45263,40 +45275,26 @@
       <c r="E192" t="b">
         <v>0</v>
       </c>
-      <c r="F192" t="n">
-        <v>0.4379999999999999</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="H192" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="I192" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="J192" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K192" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L192" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Quebec</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>46139</v>
+        <v>45775</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -45306,25 +45304,25 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0.42</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="G193" t="n">
-        <v>0.21</v>
+        <v>0.413</v>
       </c>
       <c r="H193" t="n">
-        <v>0.22</v>
+        <v>0.063</v>
       </c>
       <c r="I193" t="n">
-        <v>0.09</v>
+        <v>0.063</v>
       </c>
       <c r="J193" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="K193" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="L193" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -45334,11 +45332,11 @@
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -45348,23 +45346,25 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="G194" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H194" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="I194" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="J194" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L194" t="n">
         <v>0.02</v>
-      </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="195">
@@ -45374,7 +45374,7 @@
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>45971</v>
+        <v>46132</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -45388,13 +45388,13 @@
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="G195" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="H195" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="I195" t="n">
         <v>0.05</v>
@@ -45414,7 +45414,7 @@
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>45915</v>
+        <v>45971</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -45428,19 +45428,19 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="G196" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H196" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J196" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="n">
@@ -45454,7 +45454,7 @@
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>45887</v>
+        <v>45915</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -45468,24 +45468,24 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G197" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H197" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="I197" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J197" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="n">
-        <v>0</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -45494,7 +45494,7 @@
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>45830</v>
+        <v>45887</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -45508,24 +45508,24 @@
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G198" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="H198" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="I198" t="n">
         <v>0.05</v>
       </c>
       <c r="J198" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="n">
-        <v>0</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -45534,11 +45534,11 @@
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>45775</v>
+        <v>45830</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -45548,39 +45548,37 @@
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>0.426</v>
+        <v>0.44</v>
       </c>
       <c r="G199" t="n">
-        <v>0.233</v>
+        <v>0.23</v>
       </c>
       <c r="H199" t="n">
-        <v>0.277</v>
+        <v>0.25</v>
       </c>
       <c r="I199" t="n">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="J199" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="K199" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L199" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Quebec</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>45802</v>
+        <v>45775</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -45590,21 +45588,25 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0.54</v>
+        <v>0.426</v>
       </c>
       <c r="G200" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H200" t="inlineStr"/>
+        <v>0.233</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.277</v>
+      </c>
       <c r="I200" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="J200" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K200" t="inlineStr"/>
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0.002</v>
+      </c>
       <c r="L200" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="201">
@@ -45614,11 +45616,11 @@
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>45775</v>
+        <v>45802</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -45628,37 +45630,35 @@
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="G201" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="J201" t="n">
-        <v>0.012</v>
+        <v>0.03</v>
       </c>
       <c r="K201" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L201" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Manitoba</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>46094</v>
+        <v>45775</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Probe Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -45668,19 +45668,23 @@
         <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="G202" t="n">
-        <v>0.39</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
+        <v>0.049</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0.002</v>
+      </c>
       <c r="L202" t="n">
-        <v>0.05</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -45690,7 +45694,7 @@
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>46001</v>
+        <v>46094</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -45704,20 +45708,20 @@
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="G203" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="K203" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -45726,11 +45730,11 @@
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>45775</v>
+        <v>46001</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Probe Research</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -45740,37 +45744,33 @@
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>0.408</v>
+        <v>0.43</v>
       </c>
       <c r="G204" t="n">
-        <v>0.463</v>
+        <v>0.38</v>
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J204" t="n">
-        <v>0.006999999999999999</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="J204" t="inlineStr"/>
       <c r="K204" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L204" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Alberta</t>
+          <t>Manitoba</t>
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>46134</v>
+        <v>45775</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -45780,23 +45780,23 @@
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>0.403</v>
+        <v>0.408</v>
       </c>
       <c r="G205" t="n">
-        <v>0.458</v>
+        <v>0.463</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J205" t="n">
-        <v>0.011</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="K205" t="n">
-        <v>0.025</v>
+        <v>0.002</v>
       </c>
       <c r="L205" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="206">
@@ -45806,11 +45806,11 @@
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>46078</v>
+        <v>46134</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -45820,23 +45820,23 @@
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>0.36</v>
+        <v>0.403</v>
       </c>
       <c r="G206" t="n">
-        <v>0.51</v>
+        <v>0.458</v>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="J206" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="K206" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="L206" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="207">
@@ -45846,11 +45846,11 @@
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>46065</v>
+        <v>46078</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -45860,23 +45860,23 @@
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="G207" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J207" t="n">
         <v>0.01</v>
       </c>
       <c r="K207" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L207" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="208">
@@ -45886,11 +45886,11 @@
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>45802</v>
+        <v>46065</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -45900,21 +45900,23 @@
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="G208" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
         <v>0.05</v>
       </c>
       <c r="J208" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K208" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L208" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="209">
@@ -45924,11 +45926,11 @@
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>45775</v>
+        <v>45802</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -45938,37 +45940,35 @@
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>0.279</v>
+        <v>0.35</v>
       </c>
       <c r="G209" t="n">
-        <v>0.635</v>
+        <v>0.54</v>
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
-        <v>0.063</v>
+        <v>0.05</v>
       </c>
       <c r="J209" t="n">
-        <v>0.004</v>
+        <v>0.03</v>
       </c>
       <c r="K209" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0.008</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>British Columbia</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>46125</v>
+        <v>45775</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -45978,23 +45978,23 @@
         <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>0.512</v>
+        <v>0.279</v>
       </c>
       <c r="G210" t="n">
-        <v>0.322</v>
+        <v>0.635</v>
       </c>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="J210" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.004</v>
       </c>
       <c r="K210" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="L210" t="n">
-        <v>0.032</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -46004,7 +46004,7 @@
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>46094</v>
+        <v>46125</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -46018,23 +46018,23 @@
         <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>0.467</v>
+        <v>0.512</v>
       </c>
       <c r="G211" t="n">
-        <v>0.341</v>
+        <v>0.322</v>
       </c>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
-        <v>0.096</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="J211" t="n">
-        <v>0.039</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K211" t="n">
-        <v>0.014</v>
+        <v>0.032</v>
       </c>
       <c r="L211" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -46044,11 +46044,11 @@
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>45775</v>
+        <v>46094</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -46058,23 +46058,63 @@
         <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>0.418</v>
+        <v>0.467</v>
       </c>
       <c r="G212" t="n">
-        <v>0.41</v>
+        <v>0.341</v>
       </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="n">
+        <v>45775</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2025 election</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E213" t="b">
+        <v>0</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="n">
         <v>0.13</v>
       </c>
-      <c r="J212" t="n">
+      <c r="J213" t="n">
         <v>0.03</v>
       </c>
-      <c r="K212" t="n">
+      <c r="K213" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L213" t="n">
         <v>0.005</v>
-      </c>
-      <c r="L212" t="n">
-        <v>0.006</v>
       </c>
     </row>
   </sheetData>
